--- a/research/traditional_assets/database/data/colombia/colombia_building_materials.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_building_materials.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1090672306419366</v>
+        <v>0.1087147453346898</v>
       </c>
       <c r="C2">
-        <v>3815.699861470214</v>
+        <v>3797.855574447848</v>
       </c>
       <c r="D2">
-        <v>3693.599861470214</v>
+        <v>3714.293574447848</v>
       </c>
       <c r="E2">
-        <v>-126.1</v>
+        <v>-87.562</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>38.538</v>
       </c>
       <c r="G2">
         <v>122.1</v>
@@ -1457,28 +1457,28 @@
         <v>215.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.9384614</v>
       </c>
       <c r="N2">
-        <v>215.4</v>
+        <v>213.4615386</v>
       </c>
       <c r="O2">
-        <v>75.39</v>
+        <v>74.71153851</v>
       </c>
       <c r="P2">
-        <v>140.01</v>
+        <v>138.75000009</v>
       </c>
       <c r="Q2">
-        <v>163.61</v>
+        <v>162.35000009</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1090672306419366</v>
+        <v>0.1094826215501918</v>
       </c>
       <c r="T2">
-        <v>0.920615294616134</v>
+        <v>0.9266597384696744</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>111.119055556123</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1087147453346898</v>
+        <v>0.108362260027443</v>
       </c>
       <c r="C3">
-        <v>3797.855574447848</v>
+        <v>3780.244470490602</v>
       </c>
       <c r="D3">
-        <v>3714.293574447848</v>
+        <v>3735.220470490602</v>
       </c>
       <c r="E3">
-        <v>-87.562</v>
+        <v>-49.024</v>
       </c>
       <c r="F3">
-        <v>38.538</v>
+        <v>77.07599999999999</v>
       </c>
       <c r="G3">
         <v>122.1</v>
@@ -1539,28 +1539,28 @@
         <v>215.4</v>
       </c>
       <c r="M3">
-        <v>1.9384614</v>
+        <v>3.8769228</v>
       </c>
       <c r="N3">
-        <v>213.4615386</v>
+        <v>211.5230772</v>
       </c>
       <c r="O3">
-        <v>74.71153851</v>
+        <v>74.03307702000001</v>
       </c>
       <c r="P3">
-        <v>138.75000009</v>
+        <v>137.49000018</v>
       </c>
       <c r="Q3">
-        <v>162.35000009</v>
+        <v>161.09000018</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1094826215501918</v>
+        <v>0.1099064898239215</v>
       </c>
       <c r="T3">
-        <v>0.9266597384696744</v>
+        <v>0.9328275383202256</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>111.119055556123</v>
+        <v>55.55952777806152</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.108362260027443</v>
+        <v>0.1080097747201963</v>
       </c>
       <c r="C4">
-        <v>3780.244470490602</v>
+        <v>3762.870513297333</v>
       </c>
       <c r="D4">
-        <v>3735.220470490602</v>
+        <v>3756.384513297333</v>
       </c>
       <c r="E4">
-        <v>-49.024</v>
+        <v>-10.486</v>
       </c>
       <c r="F4">
-        <v>77.07599999999999</v>
+        <v>115.614</v>
       </c>
       <c r="G4">
         <v>122.1</v>
@@ -1621,28 +1621,28 @@
         <v>215.4</v>
       </c>
       <c r="M4">
-        <v>3.8769228</v>
+        <v>5.8153842</v>
       </c>
       <c r="N4">
-        <v>211.5230772</v>
+        <v>209.5846158</v>
       </c>
       <c r="O4">
-        <v>74.03307702000001</v>
+        <v>73.35461552999999</v>
       </c>
       <c r="P4">
-        <v>137.49000018</v>
+        <v>136.23000027</v>
       </c>
       <c r="Q4">
-        <v>161.09000018</v>
+        <v>159.83000027</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1099064898239215</v>
+        <v>0.1103390976496869</v>
       </c>
       <c r="T4">
-        <v>0.9328275383202256</v>
+        <v>0.939122509301716</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>55.55952777806152</v>
+        <v>37.03968518537434</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1080097747201963</v>
+        <v>0.1076572894129495</v>
       </c>
       <c r="C5">
-        <v>3762.870513297333</v>
+        <v>3745.737756913286</v>
       </c>
       <c r="D5">
-        <v>3756.384513297333</v>
+        <v>3777.789756913287</v>
       </c>
       <c r="E5">
-        <v>-10.486</v>
+        <v>28.05199999999999</v>
       </c>
       <c r="F5">
-        <v>115.614</v>
+        <v>154.152</v>
       </c>
       <c r="G5">
         <v>122.1</v>
@@ -1703,28 +1703,28 @@
         <v>215.4</v>
       </c>
       <c r="M5">
-        <v>5.8153842</v>
+        <v>7.753845599999999</v>
       </c>
       <c r="N5">
-        <v>209.5846158</v>
+        <v>207.6461544</v>
       </c>
       <c r="O5">
-        <v>73.35461552999999</v>
+        <v>72.67615404</v>
       </c>
       <c r="P5">
-        <v>136.23000027</v>
+        <v>134.97000036</v>
       </c>
       <c r="Q5">
-        <v>159.83000027</v>
+        <v>158.57000036</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1103390976496869</v>
+        <v>0.1107807181384891</v>
       </c>
       <c r="T5">
-        <v>0.939122509301716</v>
+        <v>0.9455486255119876</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>37.03968518537434</v>
+        <v>27.77976388903076</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1076572894129495</v>
+        <v>0.1073048041057027</v>
       </c>
       <c r="C6">
-        <v>3745.737756913286</v>
+        <v>3728.850348318969</v>
       </c>
       <c r="D6">
-        <v>3777.789756913287</v>
+        <v>3799.440348318969</v>
       </c>
       <c r="E6">
-        <v>28.05199999999999</v>
+        <v>66.59</v>
       </c>
       <c r="F6">
-        <v>154.152</v>
+        <v>192.69</v>
       </c>
       <c r="G6">
         <v>122.1</v>
@@ -1785,28 +1785,28 @@
         <v>215.4</v>
       </c>
       <c r="M6">
-        <v>7.753845599999999</v>
+        <v>9.692307</v>
       </c>
       <c r="N6">
-        <v>207.6461544</v>
+        <v>205.707693</v>
       </c>
       <c r="O6">
-        <v>72.67615404</v>
+        <v>71.99769255</v>
       </c>
       <c r="P6">
-        <v>134.97000036</v>
+        <v>133.71000045</v>
       </c>
       <c r="Q6">
-        <v>158.57000036</v>
+        <v>157.31000045</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1107807181384891</v>
+        <v>0.1112316359007397</v>
       </c>
       <c r="T6">
-        <v>0.9455486255119876</v>
+        <v>0.9521100283793176</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>27.77976388903076</v>
+        <v>22.22381111122461</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1073048041057027</v>
+        <v>0.1069523187984559</v>
       </c>
       <c r="C7">
-        <v>3728.850348318969</v>
+        <v>3712.212530108591</v>
       </c>
       <c r="D7">
-        <v>3799.440348318969</v>
+        <v>3821.340530108591</v>
       </c>
       <c r="E7">
-        <v>66.59</v>
+        <v>105.128</v>
       </c>
       <c r="F7">
-        <v>192.69</v>
+        <v>231.228</v>
       </c>
       <c r="G7">
         <v>122.1</v>
@@ -1867,28 +1867,28 @@
         <v>215.4</v>
       </c>
       <c r="M7">
-        <v>9.692307</v>
+        <v>11.6307684</v>
       </c>
       <c r="N7">
-        <v>205.707693</v>
+        <v>203.7692316</v>
       </c>
       <c r="O7">
-        <v>71.99769255</v>
+        <v>71.31923105999999</v>
       </c>
       <c r="P7">
-        <v>133.71000045</v>
+        <v>132.45000054</v>
       </c>
       <c r="Q7">
-        <v>157.31000045</v>
+        <v>156.05000054</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1112316359007397</v>
+        <v>0.1116921476579319</v>
       </c>
       <c r="T7">
-        <v>0.9521100283793176</v>
+        <v>0.9588110355629736</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.22381111122461</v>
+        <v>18.51984259268717</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1069523187984559</v>
+        <v>0.1065998334912092</v>
       </c>
       <c r="C8">
-        <v>3712.212530108591</v>
+        <v>3695.828643261625</v>
       </c>
       <c r="D8">
-        <v>3821.340530108591</v>
+        <v>3843.494643261625</v>
       </c>
       <c r="E8">
-        <v>105.128</v>
+        <v>143.666</v>
       </c>
       <c r="F8">
-        <v>231.228</v>
+        <v>269.766</v>
       </c>
       <c r="G8">
         <v>122.1</v>
@@ -1949,28 +1949,28 @@
         <v>215.4</v>
       </c>
       <c r="M8">
-        <v>11.6307684</v>
+        <v>13.5692298</v>
       </c>
       <c r="N8">
-        <v>203.7692316</v>
+        <v>201.8307702</v>
       </c>
       <c r="O8">
-        <v>71.31923105999999</v>
+        <v>70.64076957</v>
       </c>
       <c r="P8">
-        <v>132.45000054</v>
+        <v>131.19000063</v>
       </c>
       <c r="Q8">
-        <v>156.05000054</v>
+        <v>154.79000063</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1116921476579319</v>
+        <v>0.1121625628937733</v>
       </c>
       <c r="T8">
-        <v>0.9588110355629736</v>
+        <v>0.9656561504279986</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.51984259268717</v>
+        <v>15.87415079373186</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1065998334912092</v>
+        <v>0.1062473481839624</v>
       </c>
       <c r="C9">
-        <v>3695.828643261626</v>
+        <v>3679.703130011389</v>
       </c>
       <c r="D9">
-        <v>3843.494643261626</v>
+        <v>3865.907130011389</v>
       </c>
       <c r="E9">
-        <v>143.666</v>
+        <v>182.204</v>
       </c>
       <c r="F9">
-        <v>269.766</v>
+        <v>308.304</v>
       </c>
       <c r="G9">
         <v>122.1</v>
@@ -2031,28 +2031,28 @@
         <v>215.4</v>
       </c>
       <c r="M9">
-        <v>13.5692298</v>
+        <v>15.5076912</v>
       </c>
       <c r="N9">
-        <v>201.8307702</v>
+        <v>199.8923088</v>
       </c>
       <c r="O9">
-        <v>70.64076957</v>
+        <v>69.96230808</v>
       </c>
       <c r="P9">
-        <v>131.19000063</v>
+        <v>129.93000072</v>
       </c>
       <c r="Q9">
-        <v>154.79000063</v>
+        <v>153.53000072</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1121625628937733</v>
+        <v>0.1126432045477852</v>
       </c>
       <c r="T9">
-        <v>0.9656561504279986</v>
+        <v>0.9726500721379154</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.87415079373186</v>
+        <v>13.88988194451538</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1062473481839624</v>
+        <v>0.1059826128767156</v>
       </c>
       <c r="C10">
-        <v>3679.703130011389</v>
+        <v>3658.170741149403</v>
       </c>
       <c r="D10">
-        <v>3865.907130011389</v>
+        <v>3882.912741149403</v>
       </c>
       <c r="E10">
-        <v>182.204</v>
+        <v>220.742</v>
       </c>
       <c r="F10">
-        <v>308.304</v>
+        <v>346.842</v>
       </c>
       <c r="G10">
         <v>122.1</v>
@@ -2113,45 +2113,45 @@
         <v>215.4</v>
       </c>
       <c r="M10">
-        <v>15.5076912</v>
+        <v>17.9664156</v>
       </c>
       <c r="N10">
-        <v>199.8923088</v>
+        <v>197.4335844</v>
       </c>
       <c r="O10">
-        <v>69.96230808</v>
+        <v>69.10175454</v>
       </c>
       <c r="P10">
-        <v>129.93000072</v>
+        <v>128.33182986</v>
       </c>
       <c r="Q10">
-        <v>153.53000072</v>
+        <v>151.93182986</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1126432045477852</v>
+        <v>0.1131344097546325</v>
       </c>
       <c r="T10">
-        <v>0.9726500721379154</v>
+        <v>0.9797977064128854</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.35</v>
       </c>
       <c r="W10">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.88988194451538</v>
+        <v>11.98903580968037</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1059826128767156</v>
+        <v>0.1056398775694688</v>
       </c>
       <c r="C11">
-        <v>3658.170741149403</v>
+        <v>3641.872280155903</v>
       </c>
       <c r="D11">
-        <v>3882.912741149403</v>
+        <v>3905.152280155903</v>
       </c>
       <c r="E11">
-        <v>220.742</v>
+        <v>259.28</v>
       </c>
       <c r="F11">
-        <v>346.842</v>
+        <v>385.3799999999999</v>
       </c>
       <c r="G11">
         <v>122.1</v>
@@ -2195,28 +2195,28 @@
         <v>215.4</v>
       </c>
       <c r="M11">
-        <v>17.9664156</v>
+        <v>19.962684</v>
       </c>
       <c r="N11">
-        <v>197.4335844</v>
+        <v>195.437316</v>
       </c>
       <c r="O11">
-        <v>69.10175454</v>
+        <v>68.4030606</v>
       </c>
       <c r="P11">
-        <v>128.33182986</v>
+        <v>127.0342554</v>
       </c>
       <c r="Q11">
-        <v>151.93182986</v>
+        <v>150.6342554</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1131344097546325</v>
+        <v>0.1136365306327431</v>
       </c>
       <c r="T11">
-        <v>0.9797977064128854</v>
+        <v>0.987104177005077</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.98903580968037</v>
+        <v>10.79013222871233</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1056398775694688</v>
+        <v>0.1054186922622221</v>
       </c>
       <c r="C12">
-        <v>3641.872280155903</v>
+        <v>3617.822392426674</v>
       </c>
       <c r="D12">
-        <v>3905.152280155903</v>
+        <v>3919.640392426675</v>
       </c>
       <c r="E12">
-        <v>259.28</v>
+        <v>297.818</v>
       </c>
       <c r="F12">
-        <v>385.38</v>
+        <v>423.9179999999999</v>
       </c>
       <c r="G12">
         <v>122.1</v>
@@ -2277,45 +2277,45 @@
         <v>215.4</v>
       </c>
       <c r="M12">
-        <v>19.962684</v>
+        <v>22.679613</v>
       </c>
       <c r="N12">
-        <v>195.437316</v>
+        <v>192.720387</v>
       </c>
       <c r="O12">
-        <v>68.4030606</v>
+        <v>67.45213545</v>
       </c>
       <c r="P12">
-        <v>127.0342554</v>
+        <v>125.26825155</v>
       </c>
       <c r="Q12">
-        <v>150.6342554</v>
+        <v>148.86825155</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1136365306327431</v>
+        <v>0.1141499351260922</v>
       </c>
       <c r="T12">
-        <v>0.987104177005077</v>
+        <v>0.994574837947655</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.35</v>
       </c>
       <c r="W12">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.79013222871233</v>
+        <v>9.497516558152913</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1054186922622221</v>
+        <v>0.1050870069549753</v>
       </c>
       <c r="C13">
-        <v>3617.822392426674</v>
+        <v>3601.213094761847</v>
       </c>
       <c r="D13">
-        <v>3919.640392426675</v>
+        <v>3941.569094761847</v>
       </c>
       <c r="E13">
-        <v>297.818</v>
+        <v>336.356</v>
       </c>
       <c r="F13">
-        <v>423.9179999999999</v>
+        <v>462.456</v>
       </c>
       <c r="G13">
         <v>122.1</v>
@@ -2359,28 +2359,28 @@
         <v>215.4</v>
       </c>
       <c r="M13">
-        <v>22.679613</v>
+        <v>24.741396</v>
       </c>
       <c r="N13">
-        <v>192.720387</v>
+        <v>190.658604</v>
       </c>
       <c r="O13">
-        <v>67.45213545</v>
+        <v>66.7305114</v>
       </c>
       <c r="P13">
-        <v>125.26825155</v>
+        <v>123.9280926</v>
       </c>
       <c r="Q13">
-        <v>148.86825155</v>
+        <v>147.5280926</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1141499351260922</v>
+        <v>0.114675007903381</v>
       </c>
       <c r="T13">
-        <v>0.994574837947655</v>
+        <v>1.002215286638928</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.497516558152913</v>
+        <v>8.706056844973501</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1050870069549753</v>
+        <v>0.1047553216477285</v>
       </c>
       <c r="C14">
-        <v>3601.213094761847</v>
+        <v>3584.850540840189</v>
       </c>
       <c r="D14">
-        <v>3941.569094761847</v>
+        <v>3963.744540840189</v>
       </c>
       <c r="E14">
-        <v>336.356</v>
+        <v>374.894</v>
       </c>
       <c r="F14">
-        <v>462.456</v>
+        <v>500.994</v>
       </c>
       <c r="G14">
         <v>122.1</v>
@@ -2441,28 +2441,28 @@
         <v>215.4</v>
       </c>
       <c r="M14">
-        <v>24.741396</v>
+        <v>26.803179</v>
       </c>
       <c r="N14">
-        <v>190.658604</v>
+        <v>188.596821</v>
       </c>
       <c r="O14">
-        <v>66.7305114</v>
+        <v>66.00888734999999</v>
       </c>
       <c r="P14">
-        <v>123.9280926</v>
+        <v>122.58793365</v>
       </c>
       <c r="Q14">
-        <v>147.5280926</v>
+        <v>146.18793365</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.114675007903381</v>
+        <v>0.1152121513192282</v>
       </c>
       <c r="T14">
-        <v>1.002215286638928</v>
+        <v>1.01003137782885</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.706056844973501</v>
+        <v>8.036360164590924</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1047553216477285</v>
+        <v>0.1044964363404817</v>
       </c>
       <c r="C15">
-        <v>3584.850540840189</v>
+        <v>3563.79495182253</v>
       </c>
       <c r="D15">
-        <v>3963.744540840189</v>
+        <v>3981.226951822531</v>
       </c>
       <c r="E15">
-        <v>374.894</v>
+        <v>413.432</v>
       </c>
       <c r="F15">
-        <v>500.994</v>
+        <v>539.532</v>
       </c>
       <c r="G15">
         <v>122.1</v>
@@ -2523,45 +2523,45 @@
         <v>215.4</v>
       </c>
       <c r="M15">
-        <v>26.803179</v>
+        <v>29.2965876</v>
       </c>
       <c r="N15">
-        <v>188.596821</v>
+        <v>186.1034124</v>
       </c>
       <c r="O15">
-        <v>66.00888734999999</v>
+        <v>65.13619433999999</v>
       </c>
       <c r="P15">
-        <v>122.58793365</v>
+        <v>120.96721806</v>
       </c>
       <c r="Q15">
-        <v>146.18793365</v>
+        <v>144.56721806</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1152121513192282</v>
+        <v>0.1157617864424206</v>
       </c>
       <c r="T15">
-        <v>1.01003137782885</v>
+        <v>1.01802923858133</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.35</v>
       </c>
       <c r="W15">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>8.036360164590924</v>
+        <v>7.352392126378568</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1044964363404817</v>
+        <v>0.1041699510332349</v>
       </c>
       <c r="C16">
-        <v>3563.79495182253</v>
+        <v>3547.52546638484</v>
       </c>
       <c r="D16">
-        <v>3981.226951822531</v>
+        <v>4003.495466384841</v>
       </c>
       <c r="E16">
-        <v>413.432</v>
+        <v>451.97</v>
       </c>
       <c r="F16">
-        <v>539.532</v>
+        <v>578.0700000000001</v>
       </c>
       <c r="G16">
         <v>122.1</v>
@@ -2605,28 +2605,28 @@
         <v>215.4</v>
       </c>
       <c r="M16">
-        <v>29.2965876</v>
+        <v>31.389201</v>
       </c>
       <c r="N16">
-        <v>186.1034124</v>
+        <v>184.010799</v>
       </c>
       <c r="O16">
-        <v>65.13619433999999</v>
+        <v>64.40377964999999</v>
       </c>
       <c r="P16">
-        <v>120.96721806</v>
+        <v>119.60701935</v>
       </c>
       <c r="Q16">
-        <v>144.56721806</v>
+        <v>143.20701935</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1157617864424206</v>
+        <v>0.116324354156747</v>
       </c>
       <c r="T16">
-        <v>1.01802923858133</v>
+        <v>1.026215284292691</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.352392126378568</v>
+        <v>6.862232651286662</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1041699510332349</v>
+        <v>0.1038434657259882</v>
       </c>
       <c r="C17">
-        <v>3547.525466384841</v>
+        <v>3531.506494686393</v>
       </c>
       <c r="D17">
-        <v>4003.495466384841</v>
+        <v>4026.014494686393</v>
       </c>
       <c r="E17">
-        <v>451.9699999999999</v>
+        <v>490.5079999999999</v>
       </c>
       <c r="F17">
-        <v>578.0699999999999</v>
+        <v>616.6079999999999</v>
       </c>
       <c r="G17">
         <v>122.1</v>
@@ -2687,28 +2687,28 @@
         <v>215.4</v>
       </c>
       <c r="M17">
-        <v>31.389201</v>
+        <v>33.4818144</v>
       </c>
       <c r="N17">
-        <v>184.010799</v>
+        <v>181.9181856</v>
       </c>
       <c r="O17">
-        <v>64.40377965</v>
+        <v>63.67136496</v>
       </c>
       <c r="P17">
-        <v>119.60701935</v>
+        <v>118.24682064</v>
       </c>
       <c r="Q17">
-        <v>143.20701935</v>
+        <v>141.84682064</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.116324354156747</v>
+        <v>0.1169003163404621</v>
       </c>
       <c r="T17">
-        <v>1.026215284292691</v>
+        <v>1.034596235854322</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.862232651286665</v>
+        <v>6.433343110581248</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1038434657259882</v>
+        <v>0.1036274804187414</v>
       </c>
       <c r="C18">
-        <v>3531.506494686393</v>
+        <v>3508.005635701671</v>
       </c>
       <c r="D18">
-        <v>4026.014494686393</v>
+        <v>4041.05163570167</v>
       </c>
       <c r="E18">
-        <v>490.5079999999999</v>
+        <v>529.0459999999999</v>
       </c>
       <c r="F18">
-        <v>616.6079999999999</v>
+        <v>655.146</v>
       </c>
       <c r="G18">
         <v>122.1</v>
@@ -2769,45 +2769,45 @@
         <v>215.4</v>
       </c>
       <c r="M18">
-        <v>33.4818144</v>
+        <v>36.2295738</v>
       </c>
       <c r="N18">
-        <v>181.9181856</v>
+        <v>179.1704262</v>
       </c>
       <c r="O18">
-        <v>63.67136496</v>
+        <v>62.70964917</v>
       </c>
       <c r="P18">
-        <v>118.24682064</v>
+        <v>116.46077703</v>
       </c>
       <c r="Q18">
-        <v>141.84682064</v>
+        <v>140.06077703</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1169003163404621</v>
+        <v>0.1174901571310137</v>
       </c>
       <c r="T18">
-        <v>1.034596235854322</v>
+        <v>1.043179138055993</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.35</v>
       </c>
       <c r="W18">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.433343110581248</v>
+        <v>5.945419098471427</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1036274804187414</v>
+        <v>0.1033074951114946</v>
       </c>
       <c r="C19">
-        <v>3508.005635701671</v>
+        <v>3491.953002987154</v>
       </c>
       <c r="D19">
-        <v>4041.05163570167</v>
+        <v>4063.537002987154</v>
       </c>
       <c r="E19">
-        <v>529.0459999999999</v>
+        <v>567.5840000000001</v>
       </c>
       <c r="F19">
-        <v>655.146</v>
+        <v>693.6840000000001</v>
       </c>
       <c r="G19">
         <v>122.1</v>
@@ -2851,28 +2851,28 @@
         <v>215.4</v>
       </c>
       <c r="M19">
-        <v>36.2295738</v>
+        <v>38.3607252</v>
       </c>
       <c r="N19">
-        <v>179.1704262</v>
+        <v>177.0392748</v>
       </c>
       <c r="O19">
-        <v>62.70964917</v>
+        <v>61.96374617999999</v>
       </c>
       <c r="P19">
-        <v>116.46077703</v>
+        <v>115.07552862</v>
       </c>
       <c r="Q19">
-        <v>140.06077703</v>
+        <v>138.67552862</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1174901571310137</v>
+        <v>0.1180943842823105</v>
       </c>
       <c r="T19">
-        <v>1.043179138055993</v>
+        <v>1.051971379335753</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.945419098471427</v>
+        <v>5.615118037445235</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1033074951114946</v>
+        <v>0.1029875098042478</v>
       </c>
       <c r="C20">
-        <v>3491.953002987153</v>
+        <v>3476.151998195729</v>
       </c>
       <c r="D20">
-        <v>4063.537002987153</v>
+        <v>4086.273998195728</v>
       </c>
       <c r="E20">
-        <v>567.5839999999999</v>
+        <v>606.122</v>
       </c>
       <c r="F20">
-        <v>693.684</v>
+        <v>732.222</v>
       </c>
       <c r="G20">
         <v>122.1</v>
@@ -2933,28 +2933,28 @@
         <v>215.4</v>
       </c>
       <c r="M20">
-        <v>38.3607252</v>
+        <v>40.4918766</v>
       </c>
       <c r="N20">
-        <v>177.0392748</v>
+        <v>174.9081234</v>
       </c>
       <c r="O20">
-        <v>61.96374618</v>
+        <v>61.21784319</v>
       </c>
       <c r="P20">
-        <v>115.07552862</v>
+        <v>113.69028021</v>
       </c>
       <c r="Q20">
-        <v>138.67552862</v>
+        <v>137.29028021</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1180943842823105</v>
+        <v>0.1187135306225282</v>
       </c>
       <c r="T20">
-        <v>1.051971379335753</v>
+        <v>1.060980712992792</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.615118037445236</v>
+        <v>5.319585509158645</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1029875098042478</v>
+        <v>0.1026675244970011</v>
       </c>
       <c r="C21">
-        <v>3476.151998195729</v>
+        <v>3460.606868948808</v>
       </c>
       <c r="D21">
-        <v>4086.273998195728</v>
+        <v>4109.266868948808</v>
       </c>
       <c r="E21">
-        <v>606.122</v>
+        <v>644.66</v>
       </c>
       <c r="F21">
-        <v>732.222</v>
+        <v>770.76</v>
       </c>
       <c r="G21">
         <v>122.1</v>
@@ -3015,28 +3015,28 @@
         <v>215.4</v>
       </c>
       <c r="M21">
-        <v>40.4918766</v>
+        <v>42.623028</v>
       </c>
       <c r="N21">
-        <v>174.9081234</v>
+        <v>172.776972</v>
       </c>
       <c r="O21">
-        <v>61.21784319</v>
+        <v>60.4719402</v>
       </c>
       <c r="P21">
-        <v>113.69028021</v>
+        <v>112.3050318</v>
       </c>
       <c r="Q21">
-        <v>137.29028021</v>
+        <v>135.9050318</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1187135306225282</v>
+        <v>0.1193481556212513</v>
       </c>
       <c r="T21">
-        <v>1.060980712992792</v>
+        <v>1.070215279991256</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.319585509158645</v>
+        <v>5.053606233700712</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1026675244970011</v>
+        <v>0.1023475391897543</v>
       </c>
       <c r="C22">
-        <v>3460.606868948808</v>
+        <v>3445.321959011797</v>
       </c>
       <c r="D22">
-        <v>4109.266868948808</v>
+        <v>4132.519959011796</v>
       </c>
       <c r="E22">
-        <v>644.66</v>
+        <v>683.198</v>
       </c>
       <c r="F22">
-        <v>770.76</v>
+        <v>809.298</v>
       </c>
       <c r="G22">
         <v>122.1</v>
@@ -3097,28 +3097,28 @@
         <v>215.4</v>
       </c>
       <c r="M22">
-        <v>42.623028</v>
+        <v>44.7541794</v>
       </c>
       <c r="N22">
-        <v>172.776972</v>
+        <v>170.6458206</v>
       </c>
       <c r="O22">
-        <v>60.4719402</v>
+        <v>59.72603721</v>
       </c>
       <c r="P22">
-        <v>112.3050318</v>
+        <v>110.91978339</v>
       </c>
       <c r="Q22">
-        <v>135.9050318</v>
+        <v>134.51978339</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1193481556212513</v>
+        <v>0.1199988470756383</v>
       </c>
       <c r="T22">
-        <v>1.070215279991256</v>
+        <v>1.07968363349601</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.053606233700712</v>
+        <v>4.812958317810202</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1023475391897543</v>
+        <v>0.1020275538825075</v>
       </c>
       <c r="C23">
-        <v>3445.321959011797</v>
+        <v>3430.3017110298</v>
       </c>
       <c r="D23">
-        <v>4132.519959011796</v>
+        <v>4156.0377110298</v>
       </c>
       <c r="E23">
-        <v>683.1979999999999</v>
+        <v>721.7359999999999</v>
       </c>
       <c r="F23">
-        <v>809.2979999999999</v>
+        <v>847.8359999999999</v>
       </c>
       <c r="G23">
         <v>122.1</v>
@@ -3179,28 +3179,28 @@
         <v>215.4</v>
       </c>
       <c r="M23">
-        <v>44.7541794</v>
+        <v>46.8853308</v>
       </c>
       <c r="N23">
-        <v>170.6458206</v>
+        <v>168.5146692</v>
       </c>
       <c r="O23">
-        <v>59.72603721</v>
+        <v>58.98013422</v>
       </c>
       <c r="P23">
-        <v>110.91978339</v>
+        <v>109.53453498</v>
       </c>
       <c r="Q23">
-        <v>134.51978339</v>
+        <v>133.13453498</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1199988470756383</v>
+        <v>0.1206662229262917</v>
       </c>
       <c r="T23">
-        <v>1.07968363349601</v>
+        <v>1.089394765295759</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.812958317810202</v>
+        <v>4.594187485182466</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1020275538825075</v>
+        <v>0.1020813185752607</v>
       </c>
       <c r="C24">
-        <v>3430.3017110298</v>
+        <v>3387.793511036965</v>
       </c>
       <c r="D24">
-        <v>4156.0377110298</v>
+        <v>4152.067511036965</v>
       </c>
       <c r="E24">
-        <v>721.7359999999999</v>
+        <v>760.274</v>
       </c>
       <c r="F24">
-        <v>847.8359999999999</v>
+        <v>886.374</v>
       </c>
       <c r="G24">
         <v>122.1</v>
@@ -3261,45 +3261,45 @@
         <v>215.4</v>
       </c>
       <c r="M24">
-        <v>46.8853308</v>
+        <v>51.23241720000001</v>
       </c>
       <c r="N24">
-        <v>168.5146692</v>
+        <v>164.1675828</v>
       </c>
       <c r="O24">
-        <v>58.98013422</v>
+        <v>57.45865397999999</v>
       </c>
       <c r="P24">
-        <v>109.53453498</v>
+        <v>106.70892882</v>
       </c>
       <c r="Q24">
-        <v>133.13453498</v>
+        <v>130.30892882</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1206662229262917</v>
+        <v>0.1213509332146243</v>
       </c>
       <c r="T24">
-        <v>1.089394765295759</v>
+        <v>1.099358134285111</v>
       </c>
       <c r="U24">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V24">
         <v>0.35</v>
       </c>
       <c r="W24">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.594187485182466</v>
+        <v>4.204369260172248</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1020813185752607</v>
+        <v>0.1017775832680139</v>
       </c>
       <c r="C25">
-        <v>3387.793511036965</v>
+        <v>3371.784699107411</v>
       </c>
       <c r="D25">
-        <v>4152.067511036965</v>
+        <v>4174.596699107411</v>
       </c>
       <c r="E25">
-        <v>760.274</v>
+        <v>798.812</v>
       </c>
       <c r="F25">
-        <v>886.374</v>
+        <v>924.912</v>
       </c>
       <c r="G25">
         <v>122.1</v>
@@ -3343,28 +3343,28 @@
         <v>215.4</v>
       </c>
       <c r="M25">
-        <v>51.23241720000001</v>
+        <v>53.45991360000001</v>
       </c>
       <c r="N25">
-        <v>164.1675828</v>
+        <v>161.9400864</v>
       </c>
       <c r="O25">
-        <v>57.45865397999999</v>
+        <v>56.67903023999999</v>
       </c>
       <c r="P25">
-        <v>106.70892882</v>
+        <v>105.26105616</v>
       </c>
       <c r="Q25">
-        <v>130.30892882</v>
+        <v>128.86105616</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1213509332146243</v>
+        <v>0.1220536621947552</v>
       </c>
       <c r="T25">
-        <v>1.099358134285111</v>
+        <v>1.109583697195235</v>
       </c>
       <c r="U25">
         <v>0.0578</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.204369260172248</v>
+        <v>4.029187207665071</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1017775832680139</v>
+        <v>0.1020425979607672</v>
       </c>
       <c r="C26">
-        <v>3371.784699107412</v>
+        <v>3313.576031291633</v>
       </c>
       <c r="D26">
-        <v>4174.596699107411</v>
+        <v>4154.926031291632</v>
       </c>
       <c r="E26">
-        <v>798.8119999999999</v>
+        <v>837.3499999999999</v>
       </c>
       <c r="F26">
-        <v>924.9119999999999</v>
+        <v>963.4499999999999</v>
       </c>
       <c r="G26">
         <v>122.1</v>
@@ -3425,45 +3425,45 @@
         <v>215.4</v>
       </c>
       <c r="M26">
-        <v>53.4599136</v>
+        <v>59.059485</v>
       </c>
       <c r="N26">
-        <v>161.9400864</v>
+        <v>156.340515</v>
       </c>
       <c r="O26">
-        <v>56.67903024</v>
+        <v>54.71918025</v>
       </c>
       <c r="P26">
-        <v>105.26105616</v>
+        <v>101.62133475</v>
       </c>
       <c r="Q26">
-        <v>128.86105616</v>
+        <v>125.22133475</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1220536621947552</v>
+        <v>0.1227751306143562</v>
       </c>
       <c r="T26">
-        <v>1.109583697195235</v>
+        <v>1.120081941782963</v>
       </c>
       <c r="U26">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V26">
         <v>0.35</v>
       </c>
       <c r="W26">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.029187207665072</v>
+        <v>3.647170306344528</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1020425979607672</v>
+        <v>0.1017616126535204</v>
       </c>
       <c r="C27">
-        <v>3313.576031291633</v>
+        <v>3295.900067107479</v>
       </c>
       <c r="D27">
-        <v>4154.926031291632</v>
+        <v>4175.788067107478</v>
       </c>
       <c r="E27">
-        <v>837.3499999999999</v>
+        <v>875.8879999999999</v>
       </c>
       <c r="F27">
-        <v>963.4499999999999</v>
+        <v>1001.988</v>
       </c>
       <c r="G27">
         <v>122.1</v>
@@ -3507,28 +3507,28 @@
         <v>215.4</v>
       </c>
       <c r="M27">
-        <v>59.059485</v>
+        <v>61.4218644</v>
       </c>
       <c r="N27">
-        <v>156.340515</v>
+        <v>153.9781356</v>
       </c>
       <c r="O27">
-        <v>54.71918025</v>
+        <v>53.89234746</v>
       </c>
       <c r="P27">
-        <v>101.62133475</v>
+        <v>100.08578814</v>
       </c>
       <c r="Q27">
-        <v>125.22133475</v>
+        <v>123.68578814</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1227751306143562</v>
+        <v>0.1235160981804329</v>
       </c>
       <c r="T27">
-        <v>1.120081941782963</v>
+        <v>1.1308639227109</v>
       </c>
       <c r="U27">
         <v>0.0613</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.647170306344528</v>
+        <v>3.506894525331276</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1017616126535204</v>
+        <v>0.1019720273462736</v>
       </c>
       <c r="C28">
-        <v>3295.900067107479</v>
+        <v>3241.719990354104</v>
       </c>
       <c r="D28">
-        <v>4175.788067107478</v>
+        <v>4160.145990354104</v>
       </c>
       <c r="E28">
-        <v>875.8879999999999</v>
+        <v>914.426</v>
       </c>
       <c r="F28">
-        <v>1001.988</v>
+        <v>1040.526</v>
       </c>
       <c r="G28">
         <v>122.1</v>
@@ -3589,45 +3589,45 @@
         <v>215.4</v>
       </c>
       <c r="M28">
-        <v>61.4218644</v>
+        <v>66.69771660000001</v>
       </c>
       <c r="N28">
-        <v>153.9781356</v>
+        <v>148.7022834</v>
       </c>
       <c r="O28">
-        <v>53.89234746</v>
+        <v>52.04579919</v>
       </c>
       <c r="P28">
-        <v>100.08578814</v>
+        <v>96.65648421</v>
       </c>
       <c r="Q28">
-        <v>123.68578814</v>
+        <v>120.25648421</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1235160981804329</v>
+        <v>0.1242773662277721</v>
       </c>
       <c r="T28">
-        <v>1.1308639227109</v>
+        <v>1.141941300376588</v>
       </c>
       <c r="U28">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V28">
         <v>0.35</v>
       </c>
       <c r="W28">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.506894525331276</v>
+        <v>3.229495865530125</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1019720273462736</v>
+        <v>0.1017092420390268</v>
       </c>
       <c r="C29">
-        <v>3241.719990354104</v>
+        <v>3222.73555971753</v>
       </c>
       <c r="D29">
-        <v>4160.145990354104</v>
+        <v>4179.69955971753</v>
       </c>
       <c r="E29">
-        <v>914.426</v>
+        <v>952.9640000000001</v>
       </c>
       <c r="F29">
-        <v>1040.526</v>
+        <v>1079.064</v>
       </c>
       <c r="G29">
         <v>122.1</v>
@@ -3671,28 +3671,28 @@
         <v>215.4</v>
       </c>
       <c r="M29">
-        <v>66.69771660000001</v>
+        <v>69.16800240000001</v>
       </c>
       <c r="N29">
-        <v>148.7022834</v>
+        <v>146.2319976</v>
       </c>
       <c r="O29">
-        <v>52.04579919</v>
+        <v>51.18119916</v>
       </c>
       <c r="P29">
-        <v>96.65648421</v>
+        <v>95.05079843999999</v>
       </c>
       <c r="Q29">
-        <v>120.25648421</v>
+        <v>118.65079844</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1242773662277721</v>
+        <v>0.1250597806097595</v>
       </c>
       <c r="T29">
-        <v>1.141941300376588</v>
+        <v>1.153326382977435</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.229495865530125</v>
+        <v>3.114156727475478</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1017092420390268</v>
+        <v>0.1014464567317801</v>
       </c>
       <c r="C30">
-        <v>3222.73555971753</v>
+        <v>3203.935808970196</v>
       </c>
       <c r="D30">
-        <v>4179.69955971753</v>
+        <v>4199.437808970196</v>
       </c>
       <c r="E30">
-        <v>952.9640000000001</v>
+        <v>991.5020000000001</v>
       </c>
       <c r="F30">
-        <v>1079.064</v>
+        <v>1117.602</v>
       </c>
       <c r="G30">
         <v>122.1</v>
@@ -3753,28 +3753,28 @@
         <v>215.4</v>
       </c>
       <c r="M30">
-        <v>69.16800240000001</v>
+        <v>71.63828820000001</v>
       </c>
       <c r="N30">
-        <v>146.2319976</v>
+        <v>143.7617118</v>
       </c>
       <c r="O30">
-        <v>51.18119916</v>
+        <v>50.31659913</v>
       </c>
       <c r="P30">
-        <v>95.05079843999999</v>
+        <v>93.44511267</v>
       </c>
       <c r="Q30">
-        <v>118.65079844</v>
+        <v>117.04511267</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1250597806097595</v>
+        <v>0.125864234833493</v>
       </c>
       <c r="T30">
-        <v>1.153326382977435</v>
+        <v>1.165032172130418</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.114156727475478</v>
+        <v>3.006772012734944</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1014464567317801</v>
+        <v>0.1027046714245333</v>
       </c>
       <c r="C31">
-        <v>3203.935808970196</v>
+        <v>3072.544371453084</v>
       </c>
       <c r="D31">
-        <v>4199.437808970196</v>
+        <v>4106.584371453084</v>
       </c>
       <c r="E31">
-        <v>991.5019999999998</v>
+        <v>1030.04</v>
       </c>
       <c r="F31">
-        <v>1117.602</v>
+        <v>1156.14</v>
       </c>
       <c r="G31">
         <v>122.1</v>
@@ -3835,45 +3835,45 @@
         <v>215.4</v>
       </c>
       <c r="M31">
-        <v>71.63828819999999</v>
+        <v>83.12646599999999</v>
       </c>
       <c r="N31">
-        <v>143.7617118</v>
+        <v>132.273534</v>
       </c>
       <c r="O31">
-        <v>50.31659913</v>
+        <v>46.2957369</v>
       </c>
       <c r="P31">
-        <v>93.44511267</v>
+        <v>85.9777971</v>
       </c>
       <c r="Q31">
-        <v>117.04511267</v>
+        <v>109.5777971</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.125864234833493</v>
+        <v>0.126691673463619</v>
       </c>
       <c r="T31">
-        <v>1.165032172130418</v>
+        <v>1.177072412402057</v>
       </c>
       <c r="U31">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V31">
         <v>0.35</v>
       </c>
       <c r="W31">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>3.006772012734944</v>
+        <v>2.591232496278622</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1027046714245333</v>
+        <v>0.1024925861172865</v>
       </c>
       <c r="C32">
-        <v>3072.544371453084</v>
+        <v>3049.368983529956</v>
       </c>
       <c r="D32">
-        <v>4106.584371453084</v>
+        <v>4121.946983529955</v>
       </c>
       <c r="E32">
-        <v>1030.04</v>
+        <v>1068.578</v>
       </c>
       <c r="F32">
-        <v>1156.14</v>
+        <v>1194.678</v>
       </c>
       <c r="G32">
         <v>122.1</v>
@@ -3917,28 +3917,28 @@
         <v>215.4</v>
       </c>
       <c r="M32">
-        <v>83.12646599999999</v>
+        <v>85.8973482</v>
       </c>
       <c r="N32">
-        <v>132.273534</v>
+        <v>129.5026518</v>
       </c>
       <c r="O32">
-        <v>46.2957369</v>
+        <v>45.32592813000001</v>
       </c>
       <c r="P32">
-        <v>85.9777971</v>
+        <v>84.17672367000002</v>
       </c>
       <c r="Q32">
-        <v>109.5777971</v>
+        <v>107.77672367</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.126691673463619</v>
+        <v>0.1275430958221543</v>
       </c>
       <c r="T32">
-        <v>1.177072412402057</v>
+        <v>1.189461645145338</v>
       </c>
       <c r="U32">
         <v>0.07190000000000001</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.591232496278622</v>
+        <v>2.507644351237377</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1024925861172865</v>
+        <v>0.1030917008100397</v>
       </c>
       <c r="C33">
-        <v>3049.368983529956</v>
+        <v>2967.726677571738</v>
       </c>
       <c r="D33">
-        <v>4121.946983529955</v>
+        <v>4078.842677571738</v>
       </c>
       <c r="E33">
-        <v>1068.578</v>
+        <v>1107.116</v>
       </c>
       <c r="F33">
-        <v>1194.678</v>
+        <v>1233.216</v>
       </c>
       <c r="G33">
         <v>122.1</v>
@@ -3999,45 +3999,45 @@
         <v>215.4</v>
       </c>
       <c r="M33">
-        <v>85.8973482</v>
+        <v>93.4777728</v>
       </c>
       <c r="N33">
-        <v>129.5026518</v>
+        <v>121.9222272</v>
       </c>
       <c r="O33">
-        <v>45.32592813000001</v>
+        <v>42.67277952</v>
       </c>
       <c r="P33">
-        <v>84.17672367000002</v>
+        <v>79.24944768</v>
       </c>
       <c r="Q33">
-        <v>107.77672367</v>
+        <v>102.84944768</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1275430958221543</v>
+        <v>0.1284195600147643</v>
       </c>
       <c r="T33">
-        <v>1.189461645145338</v>
+        <v>1.202215267086951</v>
       </c>
       <c r="U33">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V33">
         <v>0.35</v>
       </c>
       <c r="W33">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.507644351237377</v>
+        <v>2.304291100953574</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1030917008100397</v>
+        <v>0.1029049655027929</v>
       </c>
       <c r="C34">
-        <v>2967.726677571738</v>
+        <v>2942.526640985277</v>
       </c>
       <c r="D34">
-        <v>4078.842677571738</v>
+        <v>4092.180640985276</v>
       </c>
       <c r="E34">
-        <v>1107.116</v>
+        <v>1145.654</v>
       </c>
       <c r="F34">
-        <v>1233.216</v>
+        <v>1271.754</v>
       </c>
       <c r="G34">
         <v>122.1</v>
@@ -4081,28 +4081,28 @@
         <v>215.4</v>
       </c>
       <c r="M34">
-        <v>93.4777728</v>
+        <v>96.39895319999999</v>
       </c>
       <c r="N34">
-        <v>121.9222272</v>
+        <v>119.0010468</v>
       </c>
       <c r="O34">
-        <v>42.67277952</v>
+        <v>41.65036638</v>
       </c>
       <c r="P34">
-        <v>79.24944768</v>
+        <v>77.35068042</v>
       </c>
       <c r="Q34">
-        <v>102.84944768</v>
+        <v>100.95068042</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1284195600147643</v>
+        <v>0.1293221873176014</v>
       </c>
       <c r="T34">
-        <v>1.202215267086951</v>
+        <v>1.21534959416115</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.304291100953574</v>
+        <v>2.234464097894374</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1029049655027929</v>
+        <v>0.1027182301955462</v>
       </c>
       <c r="C35">
-        <v>2942.526640985277</v>
+        <v>2917.414121831718</v>
       </c>
       <c r="D35">
-        <v>4092.180640985276</v>
+        <v>4105.606121831717</v>
       </c>
       <c r="E35">
-        <v>1145.654</v>
+        <v>1184.192</v>
       </c>
       <c r="F35">
-        <v>1271.754</v>
+        <v>1310.292</v>
       </c>
       <c r="G35">
         <v>122.1</v>
@@ -4163,28 +4163,28 @@
         <v>215.4</v>
       </c>
       <c r="M35">
-        <v>96.39895319999999</v>
+        <v>99.32013360000001</v>
       </c>
       <c r="N35">
-        <v>119.0010468</v>
+        <v>116.0798664</v>
       </c>
       <c r="O35">
-        <v>41.65036638</v>
+        <v>40.62795324</v>
       </c>
       <c r="P35">
-        <v>77.35068042</v>
+        <v>75.45191316</v>
       </c>
       <c r="Q35">
-        <v>100.95068042</v>
+        <v>99.05191316</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1293221873176014</v>
+        <v>0.1302521669629488</v>
       </c>
       <c r="T35">
-        <v>1.21534959416115</v>
+        <v>1.228881931146688</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.234464097894374</v>
+        <v>2.168744565603363</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1027182301955462</v>
+        <v>0.1025314948882994</v>
       </c>
       <c r="C36">
-        <v>2917.414121831718</v>
+        <v>2892.389984318578</v>
       </c>
       <c r="D36">
-        <v>4105.606121831717</v>
+        <v>4119.119984318578</v>
       </c>
       <c r="E36">
-        <v>1184.192</v>
+        <v>1222.73</v>
       </c>
       <c r="F36">
-        <v>1310.292</v>
+        <v>1348.83</v>
       </c>
       <c r="G36">
         <v>122.1</v>
@@ -4245,28 +4245,28 @@
         <v>215.4</v>
       </c>
       <c r="M36">
-        <v>99.32013360000001</v>
+        <v>102.241314</v>
       </c>
       <c r="N36">
-        <v>116.0798664</v>
+        <v>113.158686</v>
       </c>
       <c r="O36">
-        <v>40.62795324</v>
+        <v>39.6055401</v>
       </c>
       <c r="P36">
-        <v>75.45191316</v>
+        <v>73.5531459</v>
       </c>
       <c r="Q36">
-        <v>99.05191316</v>
+        <v>97.1531459</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1302521669629488</v>
+        <v>0.1312107613666144</v>
       </c>
       <c r="T36">
-        <v>1.228881931146688</v>
+        <v>1.242830647731781</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.168744565603363</v>
+        <v>2.106780435157553</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1025314948882994</v>
+        <v>0.1023447595810526</v>
       </c>
       <c r="C37">
-        <v>2892.389984318578</v>
+        <v>2867.455104069321</v>
       </c>
       <c r="D37">
-        <v>4119.119984318578</v>
+        <v>4132.723104069321</v>
       </c>
       <c r="E37">
-        <v>1222.73</v>
+        <v>1261.268</v>
       </c>
       <c r="F37">
-        <v>1348.83</v>
+        <v>1387.368</v>
       </c>
       <c r="G37">
         <v>122.1</v>
@@ -4327,28 +4327,28 @@
         <v>215.4</v>
       </c>
       <c r="M37">
-        <v>102.241314</v>
+        <v>105.1624944</v>
       </c>
       <c r="N37">
-        <v>113.158686</v>
+        <v>110.2375056</v>
       </c>
       <c r="O37">
-        <v>39.6055401</v>
+        <v>38.58312695999999</v>
       </c>
       <c r="P37">
-        <v>73.5531459</v>
+        <v>71.65437864</v>
       </c>
       <c r="Q37">
-        <v>97.1531459</v>
+        <v>95.25437864</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1312107613666144</v>
+        <v>0.1321993118453947</v>
       </c>
       <c r="T37">
-        <v>1.242830647731781</v>
+        <v>1.257215261710158</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.106780435157553</v>
+        <v>2.048258756403176</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1023447595810526</v>
+        <v>0.1055731242738058</v>
       </c>
       <c r="C38">
-        <v>2867.45510406932</v>
+        <v>2605.707467360576</v>
       </c>
       <c r="D38">
-        <v>4132.72310406932</v>
+        <v>3909.513467360576</v>
       </c>
       <c r="E38">
-        <v>1261.268</v>
+        <v>1299.806</v>
       </c>
       <c r="F38">
-        <v>1387.368</v>
+        <v>1425.906</v>
       </c>
       <c r="G38">
         <v>122.1</v>
@@ -4409,45 +4409,45 @@
         <v>215.4</v>
       </c>
       <c r="M38">
-        <v>105.1624944</v>
+        <v>128.33154</v>
       </c>
       <c r="N38">
-        <v>110.2375056</v>
+        <v>87.06846000000002</v>
       </c>
       <c r="O38">
-        <v>38.58312696</v>
+        <v>30.473961</v>
       </c>
       <c r="P38">
-        <v>71.65437864</v>
+        <v>56.59449900000001</v>
       </c>
       <c r="Q38">
-        <v>95.25437864</v>
+        <v>80.19449900000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1321993118453947</v>
+        <v>0.1332192448790569</v>
       </c>
       <c r="T38">
-        <v>1.257215261710158</v>
+        <v>1.272056530100547</v>
       </c>
       <c r="U38">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V38">
         <v>0.35</v>
       </c>
       <c r="W38">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.048258756403176</v>
+        <v>1.678465013355252</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1055731242738058</v>
+        <v>0.1054786889665591</v>
       </c>
       <c r="C39">
-        <v>2605.707467360576</v>
+        <v>2573.355865082591</v>
       </c>
       <c r="D39">
-        <v>3909.513467360576</v>
+        <v>3915.699865082591</v>
       </c>
       <c r="E39">
-        <v>1299.806</v>
+        <v>1338.344</v>
       </c>
       <c r="F39">
-        <v>1425.906</v>
+        <v>1464.444</v>
       </c>
       <c r="G39">
         <v>122.1</v>
@@ -4491,28 +4491,28 @@
         <v>215.4</v>
       </c>
       <c r="M39">
-        <v>128.33154</v>
+        <v>131.79996</v>
       </c>
       <c r="N39">
-        <v>87.06846000000002</v>
+        <v>83.60004000000001</v>
       </c>
       <c r="O39">
-        <v>30.473961</v>
+        <v>29.260014</v>
       </c>
       <c r="P39">
-        <v>56.59449900000001</v>
+        <v>54.34002600000001</v>
       </c>
       <c r="Q39">
-        <v>80.19449900000001</v>
+        <v>77.940026</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1332192448790569</v>
+        <v>0.1342720789783211</v>
       </c>
       <c r="T39">
-        <v>1.272056530100547</v>
+        <v>1.287376549084174</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.678465013355252</v>
+        <v>1.63429488142485</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1054786889665591</v>
+        <v>0.1053842536593123</v>
       </c>
       <c r="C40">
-        <v>2573.355865082591</v>
+        <v>2541.023872494542</v>
       </c>
       <c r="D40">
-        <v>3915.699865082591</v>
+        <v>3921.905872494542</v>
       </c>
       <c r="E40">
-        <v>1338.344</v>
+        <v>1376.882</v>
       </c>
       <c r="F40">
-        <v>1464.444</v>
+        <v>1502.982</v>
       </c>
       <c r="G40">
         <v>122.1</v>
@@ -4573,28 +4573,28 @@
         <v>215.4</v>
       </c>
       <c r="M40">
-        <v>131.79996</v>
+        <v>135.26838</v>
       </c>
       <c r="N40">
-        <v>83.60004000000001</v>
+        <v>80.13162000000003</v>
       </c>
       <c r="O40">
-        <v>29.260014</v>
+        <v>28.04606700000001</v>
       </c>
       <c r="P40">
-        <v>54.34002600000001</v>
+        <v>52.08555300000002</v>
       </c>
       <c r="Q40">
-        <v>77.940026</v>
+        <v>75.68555300000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1342720789783211</v>
+        <v>0.1353594322283808</v>
       </c>
       <c r="T40">
-        <v>1.287376549084174</v>
+        <v>1.303198863772183</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.63429488142485</v>
+        <v>1.592389884465239</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1053842536593123</v>
+        <v>0.1052898183520655</v>
       </c>
       <c r="C41">
-        <v>2541.023872494542</v>
+        <v>2508.71158298285</v>
       </c>
       <c r="D41">
-        <v>3921.905872494542</v>
+        <v>3928.13158298285</v>
       </c>
       <c r="E41">
-        <v>1376.882</v>
+        <v>1415.42</v>
       </c>
       <c r="F41">
-        <v>1502.982</v>
+        <v>1541.52</v>
       </c>
       <c r="G41">
         <v>122.1</v>
@@ -4655,28 +4655,28 @@
         <v>215.4</v>
       </c>
       <c r="M41">
-        <v>135.26838</v>
+        <v>138.7368</v>
       </c>
       <c r="N41">
-        <v>80.13162000000003</v>
+        <v>76.66320000000002</v>
       </c>
       <c r="O41">
-        <v>28.04606700000001</v>
+        <v>26.83212</v>
       </c>
       <c r="P41">
-        <v>52.08555300000002</v>
+        <v>49.83108000000001</v>
       </c>
       <c r="Q41">
-        <v>75.68555300000001</v>
+        <v>73.43108000000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1353594322283808</v>
+        <v>0.1364830305867758</v>
       </c>
       <c r="T41">
-        <v>1.303198863772183</v>
+        <v>1.319548588949792</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.592389884465239</v>
+        <v>1.552580137353608</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1052898183520655</v>
+        <v>0.1051953830448187</v>
       </c>
       <c r="C42">
-        <v>2508.71158298285</v>
+        <v>2476.419090527853</v>
       </c>
       <c r="D42">
-        <v>3928.13158298285</v>
+        <v>3934.377090527853</v>
       </c>
       <c r="E42">
-        <v>1415.42</v>
+        <v>1453.958</v>
       </c>
       <c r="F42">
-        <v>1541.52</v>
+        <v>1580.058</v>
       </c>
       <c r="G42">
         <v>122.1</v>
@@ -4737,28 +4737,28 @@
         <v>215.4</v>
       </c>
       <c r="M42">
-        <v>138.7368</v>
+        <v>142.20522</v>
       </c>
       <c r="N42">
-        <v>76.66320000000002</v>
+        <v>73.19478000000001</v>
       </c>
       <c r="O42">
-        <v>26.83212</v>
+        <v>25.618173</v>
       </c>
       <c r="P42">
-        <v>49.83108000000001</v>
+        <v>47.57660700000001</v>
       </c>
       <c r="Q42">
-        <v>73.43108000000001</v>
+        <v>71.176607</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1364830305867758</v>
+        <v>0.1376447170251165</v>
       </c>
       <c r="T42">
-        <v>1.319548588949792</v>
+        <v>1.336452542099523</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.552580137353608</v>
+        <v>1.514712329125471</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1051953830448187</v>
+        <v>0.1234937548686074</v>
       </c>
       <c r="C43">
-        <v>2476.419090527853</v>
+        <v>1511.2597035293</v>
       </c>
       <c r="D43">
-        <v>3934.377090527853</v>
+        <v>3007.7557035293</v>
       </c>
       <c r="E43">
-        <v>1453.958</v>
+        <v>1492.496</v>
       </c>
       <c r="F43">
-        <v>1580.058</v>
+        <v>1618.596</v>
       </c>
       <c r="G43">
         <v>122.1</v>
@@ -4819,45 +4819,45 @@
         <v>215.4</v>
       </c>
       <c r="M43">
-        <v>142.20522</v>
+        <v>237.6098928</v>
       </c>
       <c r="N43">
-        <v>73.19478000000001</v>
+        <v>-22.20989280000001</v>
       </c>
       <c r="O43">
-        <v>25.618173</v>
+        <v>-7.773462480000002</v>
       </c>
       <c r="P43">
-        <v>47.57660700000001</v>
+        <v>-14.43643032</v>
       </c>
       <c r="Q43">
-        <v>71.176607</v>
+        <v>9.163569679999991</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1376447170251165</v>
+        <v>0.1403452837918325</v>
       </c>
       <c r="T43">
-        <v>1.336452542099523</v>
+        <v>1.375749079095768</v>
       </c>
       <c r="U43">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.35</v>
+        <v>0.3172847692139525</v>
       </c>
       <c r="W43">
-        <v>0.0585</v>
+        <v>0.1002225958793918</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y43">
-        <v>1.514712329125471</v>
+        <v>0.9065279120398644</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1234937548686074</v>
+        <v>0.1245037548686074</v>
       </c>
       <c r="C44">
-        <v>1511.2597035293</v>
+        <v>1434.123376605304</v>
       </c>
       <c r="D44">
-        <v>3007.7557035293</v>
+        <v>2969.157376605303</v>
       </c>
       <c r="E44">
-        <v>1492.496</v>
+        <v>1531.034</v>
       </c>
       <c r="F44">
-        <v>1618.596</v>
+        <v>1657.134</v>
       </c>
       <c r="G44">
         <v>122.1</v>
@@ -4901,37 +4901,37 @@
         <v>215.4</v>
       </c>
       <c r="M44">
-        <v>237.6098928</v>
+        <v>243.2672712</v>
       </c>
       <c r="N44">
-        <v>-22.20989279999998</v>
+        <v>-27.86727119999998</v>
       </c>
       <c r="O44">
-        <v>-7.773462479999991</v>
+        <v>-9.753544919999991</v>
       </c>
       <c r="P44">
-        <v>-14.43643031999999</v>
+        <v>-18.11372627999999</v>
       </c>
       <c r="Q44">
-        <v>9.163569680000009</v>
+        <v>5.486273720000007</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1403452837918325</v>
+        <v>0.1420039729811629</v>
       </c>
       <c r="T44">
-        <v>1.375749079095768</v>
+        <v>1.399885027851835</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.3172847692139525</v>
+        <v>0.3099060536508373</v>
       </c>
       <c r="W44">
-        <v>0.1002225958793918</v>
+        <v>0.1013057913240571</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.9065279120398645</v>
+        <v>0.885445867573821</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1245037548686074</v>
+        <v>0.1255137548686074</v>
       </c>
       <c r="C45">
-        <v>1434.123376605304</v>
+        <v>1357.96515716746</v>
       </c>
       <c r="D45">
-        <v>2969.157376605303</v>
+        <v>2931.53715716746</v>
       </c>
       <c r="E45">
-        <v>1531.034</v>
+        <v>1569.572</v>
       </c>
       <c r="F45">
-        <v>1657.134</v>
+        <v>1695.672</v>
       </c>
       <c r="G45">
         <v>122.1</v>
@@ -4983,37 +4983,37 @@
         <v>215.4</v>
       </c>
       <c r="M45">
-        <v>243.2672712</v>
+        <v>248.9246496</v>
       </c>
       <c r="N45">
-        <v>-27.86727119999998</v>
+        <v>-33.52464959999998</v>
       </c>
       <c r="O45">
-        <v>-9.753544919999991</v>
+        <v>-11.73362735999999</v>
       </c>
       <c r="P45">
-        <v>-18.11372627999999</v>
+        <v>-21.79102223999998</v>
       </c>
       <c r="Q45">
-        <v>5.486273720000007</v>
+        <v>1.808977760000012</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1420039729811629</v>
+        <v>0.1437219010701123</v>
       </c>
       <c r="T45">
-        <v>1.399885027851835</v>
+        <v>1.42488297477776</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.3099060536508373</v>
+        <v>0.302862734249682</v>
       </c>
       <c r="W45">
-        <v>0.1013057913240571</v>
+        <v>0.1023397506121467</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.885445867573821</v>
+        <v>0.8653220978562343</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1255137548686074</v>
+        <v>0.1265237548686074</v>
       </c>
       <c r="C46">
-        <v>1357.96515716746</v>
+        <v>1282.748331540996</v>
       </c>
       <c r="D46">
-        <v>2931.53715716746</v>
+        <v>2894.858331540996</v>
       </c>
       <c r="E46">
-        <v>1569.572</v>
+        <v>1608.11</v>
       </c>
       <c r="F46">
-        <v>1695.672</v>
+        <v>1734.21</v>
       </c>
       <c r="G46">
         <v>122.1</v>
@@ -5065,37 +5065,37 @@
         <v>215.4</v>
       </c>
       <c r="M46">
-        <v>248.9246496</v>
+        <v>254.582028</v>
       </c>
       <c r="N46">
-        <v>-33.52464959999998</v>
+        <v>-39.182028</v>
       </c>
       <c r="O46">
-        <v>-11.73362735999999</v>
+        <v>-13.7137098</v>
       </c>
       <c r="P46">
-        <v>-21.79102223999998</v>
+        <v>-25.4683182</v>
       </c>
       <c r="Q46">
-        <v>1.808977760000012</v>
+        <v>-1.868318200000008</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1437219010701123</v>
+        <v>0.145502299271387</v>
       </c>
       <c r="T46">
-        <v>1.42488297477776</v>
+        <v>1.450789937955538</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.302862734249682</v>
+        <v>0.2961324512663557</v>
       </c>
       <c r="W46">
-        <v>0.1023397506121467</v>
+        <v>0.103327756154099</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8653220978562343</v>
+        <v>0.8460927179038734</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1265237548686074</v>
+        <v>0.1275337548686074</v>
       </c>
       <c r="C47">
-        <v>1282.748331540996</v>
+        <v>1208.43800076338</v>
       </c>
       <c r="D47">
-        <v>2894.858331540996</v>
+        <v>2859.086000763381</v>
       </c>
       <c r="E47">
-        <v>1608.11</v>
+        <v>1646.648</v>
       </c>
       <c r="F47">
-        <v>1734.21</v>
+        <v>1772.748</v>
       </c>
       <c r="G47">
         <v>122.1</v>
@@ -5147,37 +5147,37 @@
         <v>215.4</v>
       </c>
       <c r="M47">
-        <v>254.582028</v>
+        <v>260.2394064</v>
       </c>
       <c r="N47">
-        <v>-39.182028</v>
+        <v>-44.8394064</v>
       </c>
       <c r="O47">
-        <v>-13.7137098</v>
+        <v>-15.69379224</v>
       </c>
       <c r="P47">
-        <v>-25.4683182</v>
+        <v>-29.14561416</v>
       </c>
       <c r="Q47">
-        <v>-1.868318200000008</v>
+        <v>-5.545614160000007</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.145502299271387</v>
+        <v>0.1473486381467831</v>
       </c>
       <c r="T47">
-        <v>1.450789937955538</v>
+        <v>1.477656418288048</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.2961324512663557</v>
+        <v>0.2896947892823045</v>
       </c>
       <c r="W47">
-        <v>0.103327756154099</v>
+        <v>0.1042728049333577</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8460927179038734</v>
+        <v>0.8276993979494414</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1275337548686074</v>
+        <v>0.1285437548686074</v>
       </c>
       <c r="C48">
-        <v>1208.43800076338</v>
+        <v>1135.000969829185</v>
       </c>
       <c r="D48">
-        <v>2859.086000763381</v>
+        <v>2824.186969829185</v>
       </c>
       <c r="E48">
-        <v>1646.648</v>
+        <v>1685.186</v>
       </c>
       <c r="F48">
-        <v>1772.748</v>
+        <v>1811.286</v>
       </c>
       <c r="G48">
         <v>122.1</v>
@@ -5229,37 +5229,37 @@
         <v>215.4</v>
       </c>
       <c r="M48">
-        <v>260.2394064</v>
+        <v>265.8967848</v>
       </c>
       <c r="N48">
-        <v>-44.8394064</v>
+        <v>-50.49678480000003</v>
       </c>
       <c r="O48">
-        <v>-15.69379224</v>
+        <v>-17.67387468000001</v>
       </c>
       <c r="P48">
-        <v>-29.14561416</v>
+        <v>-32.82291012000002</v>
       </c>
       <c r="Q48">
-        <v>-5.545614160000007</v>
+        <v>-9.222910120000023</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1473486381467831</v>
+        <v>0.1492646501872884</v>
       </c>
       <c r="T48">
-        <v>1.477656418288048</v>
+        <v>1.505536728067067</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.2896947892823045</v>
+        <v>0.2835310703614043</v>
       </c>
       <c r="W48">
-        <v>0.1042728049333577</v>
+        <v>0.1051776388709458</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8276993979494414</v>
+        <v>0.8100887724611553</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1285437548686074</v>
+        <v>0.1577410465334699</v>
       </c>
       <c r="C49">
-        <v>1135.000969829185</v>
+        <v>359.8376368727691</v>
       </c>
       <c r="D49">
-        <v>2824.186969829185</v>
+        <v>2087.561636872769</v>
       </c>
       <c r="E49">
-        <v>1685.186</v>
+        <v>1723.724</v>
       </c>
       <c r="F49">
-        <v>1811.286</v>
+        <v>1849.824</v>
       </c>
       <c r="G49">
         <v>122.1</v>
@@ -5311,45 +5311,45 @@
         <v>215.4</v>
       </c>
       <c r="M49">
-        <v>265.8967848</v>
+        <v>371.4446592</v>
       </c>
       <c r="N49">
-        <v>-50.49678480000003</v>
+        <v>-156.0446592</v>
       </c>
       <c r="O49">
-        <v>-17.67387468000001</v>
+        <v>-54.61563072000001</v>
       </c>
       <c r="P49">
-        <v>-32.82291012000002</v>
+        <v>-101.42902848</v>
       </c>
       <c r="Q49">
-        <v>-9.222910120000023</v>
+        <v>-77.82902848000003</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1492646501872884</v>
+        <v>0.1556145312771641</v>
       </c>
       <c r="T49">
-        <v>1.505536728067067</v>
+        <v>1.59793523501955</v>
       </c>
       <c r="U49">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.2835310703614043</v>
+        <v>0.2029642858841245</v>
       </c>
       <c r="W49">
-        <v>0.1051776388709458</v>
+        <v>0.1600447713944678</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.8100887724611553</v>
+        <v>0.5798979596689271</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1577410465334699</v>
+        <v>0.1592910465334699</v>
       </c>
       <c r="C50">
-        <v>359.8376368727693</v>
+        <v>292.7888368053957</v>
       </c>
       <c r="D50">
-        <v>2087.561636872769</v>
+        <v>2059.050836805396</v>
       </c>
       <c r="E50">
-        <v>1723.724</v>
+        <v>1762.262</v>
       </c>
       <c r="F50">
-        <v>1849.824</v>
+        <v>1888.362</v>
       </c>
       <c r="G50">
         <v>122.1</v>
@@ -5393,37 +5393,37 @@
         <v>215.4</v>
       </c>
       <c r="M50">
-        <v>371.4446592</v>
+        <v>379.1830896</v>
       </c>
       <c r="N50">
-        <v>-156.0446592</v>
+        <v>-163.7830896</v>
       </c>
       <c r="O50">
-        <v>-54.61563071999999</v>
+        <v>-57.32408135999998</v>
       </c>
       <c r="P50">
-        <v>-101.42902848</v>
+        <v>-106.45900824</v>
       </c>
       <c r="Q50">
-        <v>-77.82902848000001</v>
+        <v>-82.85900823999998</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1556145312771641</v>
+        <v>0.1577677573806379</v>
       </c>
       <c r="T50">
-        <v>1.59793523501955</v>
+        <v>1.629267298451306</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.2029642858841245</v>
+        <v>0.1988221576007751</v>
       </c>
       <c r="W50">
-        <v>0.1600447713944678</v>
+        <v>0.1608765107537644</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5798979596689272</v>
+        <v>0.5680633074307859</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1592910465334699</v>
+        <v>0.1608410465334699</v>
       </c>
       <c r="C51">
-        <v>292.7888368053957</v>
+        <v>226.5083145212313</v>
       </c>
       <c r="D51">
-        <v>2059.050836805396</v>
+        <v>2031.308314521231</v>
       </c>
       <c r="E51">
-        <v>1762.262</v>
+        <v>1800.8</v>
       </c>
       <c r="F51">
-        <v>1888.362</v>
+        <v>1926.9</v>
       </c>
       <c r="G51">
         <v>122.1</v>
@@ -5475,37 +5475,37 @@
         <v>215.4</v>
       </c>
       <c r="M51">
-        <v>379.1830896</v>
+        <v>386.92152</v>
       </c>
       <c r="N51">
-        <v>-163.7830896</v>
+        <v>-171.52152</v>
       </c>
       <c r="O51">
-        <v>-57.32408135999998</v>
+        <v>-60.03253199999999</v>
       </c>
       <c r="P51">
-        <v>-106.45900824</v>
+        <v>-111.488988</v>
       </c>
       <c r="Q51">
-        <v>-82.85900823999998</v>
+        <v>-87.888988</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1577677573806379</v>
+        <v>0.1600071125282506</v>
       </c>
       <c r="T51">
-        <v>1.629267298451306</v>
+        <v>1.661852644420332</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1988221576007751</v>
+        <v>0.1948457144487595</v>
       </c>
       <c r="W51">
-        <v>0.1608765107537644</v>
+        <v>0.1616749805386891</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5680633074307859</v>
+        <v>0.5567020412821702</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1608410465334699</v>
+        <v>0.1623910465334699</v>
       </c>
       <c r="C52">
-        <v>226.5083145212313</v>
+        <v>160.9654288021209</v>
       </c>
       <c r="D52">
-        <v>2031.308314521231</v>
+        <v>2004.303428802121</v>
       </c>
       <c r="E52">
-        <v>1800.8</v>
+        <v>1839.338</v>
       </c>
       <c r="F52">
-        <v>1926.9</v>
+        <v>1965.438</v>
       </c>
       <c r="G52">
         <v>122.1</v>
@@ -5557,37 +5557,37 @@
         <v>215.4</v>
       </c>
       <c r="M52">
-        <v>386.92152</v>
+        <v>394.6599504</v>
       </c>
       <c r="N52">
-        <v>-171.52152</v>
+        <v>-179.2599504</v>
       </c>
       <c r="O52">
-        <v>-60.03253199999999</v>
+        <v>-62.74098264</v>
       </c>
       <c r="P52">
-        <v>-111.488988</v>
+        <v>-116.51896776</v>
       </c>
       <c r="Q52">
-        <v>-87.888988</v>
+        <v>-92.91896776000002</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1600071125282506</v>
+        <v>0.1623378699267864</v>
       </c>
       <c r="T52">
-        <v>1.661852644420332</v>
+        <v>1.695768004510543</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1948457144487595</v>
+        <v>0.1910252102438819</v>
       </c>
       <c r="W52">
-        <v>0.1616749805386891</v>
+        <v>0.1624421377830285</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5567020412821702</v>
+        <v>0.5457863149825197</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1623910465334699</v>
+        <v>0.1639410465334699</v>
       </c>
       <c r="C53">
-        <v>160.9654288021209</v>
+        <v>96.13114647011048</v>
       </c>
       <c r="D53">
-        <v>2004.303428802121</v>
+        <v>1978.00714647011</v>
       </c>
       <c r="E53">
-        <v>1839.338</v>
+        <v>1877.876</v>
       </c>
       <c r="F53">
-        <v>1965.438</v>
+        <v>2003.976</v>
       </c>
       <c r="G53">
         <v>122.1</v>
@@ -5639,37 +5639,37 @@
         <v>215.4</v>
       </c>
       <c r="M53">
-        <v>394.6599504</v>
+        <v>402.3983808</v>
       </c>
       <c r="N53">
-        <v>-179.2599504</v>
+        <v>-186.9983808</v>
       </c>
       <c r="O53">
-        <v>-62.74098264</v>
+        <v>-65.44943327999999</v>
       </c>
       <c r="P53">
-        <v>-116.51896776</v>
+        <v>-121.54894752</v>
       </c>
       <c r="Q53">
-        <v>-92.91896776000002</v>
+        <v>-97.94894751999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1623378699267864</v>
+        <v>0.1647657422169278</v>
       </c>
       <c r="T53">
-        <v>1.695768004510543</v>
+        <v>1.731096504604513</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1910252102438819</v>
+        <v>0.1873516485084226</v>
       </c>
       <c r="W53">
-        <v>0.1624421377830285</v>
+        <v>0.1631797889795087</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5457863149825197</v>
+        <v>0.5352904243097789</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1639410465334699</v>
+        <v>0.1654910465334699</v>
       </c>
       <c r="C54">
-        <v>96.13114647011048</v>
+        <v>31.97793826678503</v>
       </c>
       <c r="D54">
-        <v>1978.00714647011</v>
+        <v>1952.391938266785</v>
       </c>
       <c r="E54">
-        <v>1877.876</v>
+        <v>1916.414</v>
       </c>
       <c r="F54">
-        <v>2003.976</v>
+        <v>2042.514</v>
       </c>
       <c r="G54">
         <v>122.1</v>
@@ -5721,37 +5721,37 @@
         <v>215.4</v>
       </c>
       <c r="M54">
-        <v>402.3983808</v>
+        <v>410.1368112</v>
       </c>
       <c r="N54">
-        <v>-186.9983808</v>
+        <v>-194.7368112</v>
       </c>
       <c r="O54">
-        <v>-65.44943327999999</v>
+        <v>-68.15788392</v>
       </c>
       <c r="P54">
-        <v>-121.54894752</v>
+        <v>-126.57892728</v>
       </c>
       <c r="Q54">
-        <v>-97.94894751999999</v>
+        <v>-102.97892728</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1647657422169278</v>
+        <v>0.1672969282215433</v>
       </c>
       <c r="T54">
-        <v>1.731096504604513</v>
+        <v>1.767928345128013</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1873516485084226</v>
+        <v>0.1838167117441128</v>
       </c>
       <c r="W54">
-        <v>0.1631797889795087</v>
+        <v>0.1638896042817822</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5352904243097789</v>
+        <v>0.5251906049831794</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1654910465334699</v>
+        <v>0.1670410465334699</v>
       </c>
       <c r="C55">
-        <v>31.97793826678503</v>
+        <v>-31.5203172806464</v>
       </c>
       <c r="D55">
-        <v>1952.391938266785</v>
+        <v>1927.431682719354</v>
       </c>
       <c r="E55">
-        <v>1916.414</v>
+        <v>1954.952</v>
       </c>
       <c r="F55">
-        <v>2042.514</v>
+        <v>2081.052</v>
       </c>
       <c r="G55">
         <v>122.1</v>
@@ -5803,37 +5803,37 @@
         <v>215.4</v>
       </c>
       <c r="M55">
-        <v>410.1368112</v>
+        <v>417.8752416</v>
       </c>
       <c r="N55">
-        <v>-194.7368112</v>
+        <v>-202.4752416</v>
       </c>
       <c r="O55">
-        <v>-68.15788392</v>
+        <v>-70.86633456000001</v>
       </c>
       <c r="P55">
-        <v>-126.57892728</v>
+        <v>-131.60890704</v>
       </c>
       <c r="Q55">
-        <v>-102.97892728</v>
+        <v>-108.00890704</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1672969282215433</v>
+        <v>0.1699381657915768</v>
       </c>
       <c r="T55">
-        <v>1.767928345128013</v>
+        <v>1.8063615700221</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1838167117441128</v>
+        <v>0.1804126985636662</v>
       </c>
       <c r="W55">
-        <v>0.1638896042817822</v>
+        <v>0.1645731301284158</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5251906049831794</v>
+        <v>0.5154648530390463</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1670410465334699</v>
+        <v>0.1685910465334698</v>
       </c>
       <c r="C56">
-        <v>-31.5203172806464</v>
+        <v>-94.38842271224007</v>
       </c>
       <c r="D56">
-        <v>1927.431682719354</v>
+        <v>1903.10157728776</v>
       </c>
       <c r="E56">
-        <v>1954.952</v>
+        <v>1993.49</v>
       </c>
       <c r="F56">
-        <v>2081.052</v>
+        <v>2119.59</v>
       </c>
       <c r="G56">
         <v>122.1</v>
@@ -5885,37 +5885,37 @@
         <v>215.4</v>
       </c>
       <c r="M56">
-        <v>417.8752416</v>
+        <v>425.6136720000001</v>
       </c>
       <c r="N56">
-        <v>-202.4752416</v>
+        <v>-210.2136720000001</v>
       </c>
       <c r="O56">
-        <v>-70.86633456000001</v>
+        <v>-73.57478520000002</v>
       </c>
       <c r="P56">
-        <v>-131.60890704</v>
+        <v>-136.6388868</v>
       </c>
       <c r="Q56">
-        <v>-108.00890704</v>
+        <v>-113.0388868</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1699381657915768</v>
+        <v>0.1726967916980563</v>
       </c>
       <c r="T56">
-        <v>1.8063615700221</v>
+        <v>1.846502938244813</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1804126985636662</v>
+        <v>0.1771324676806904</v>
       </c>
       <c r="W56">
-        <v>0.1645731301284158</v>
+        <v>0.1652318004897174</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5154648530390463</v>
+        <v>0.5060927648019727</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1685910465334698</v>
+        <v>0.1906559261060882</v>
       </c>
       <c r="C57">
-        <v>-94.38842271224007</v>
+        <v>-422.8124373621411</v>
       </c>
       <c r="D57">
-        <v>1903.10157728776</v>
+        <v>1613.215562637859</v>
       </c>
       <c r="E57">
-        <v>1993.49</v>
+        <v>2032.028</v>
       </c>
       <c r="F57">
-        <v>2119.59</v>
+        <v>2158.128</v>
       </c>
       <c r="G57">
         <v>122.1</v>
@@ -5967,45 +5967,45 @@
         <v>215.4</v>
       </c>
       <c r="M57">
-        <v>425.6136720000001</v>
+        <v>508.8865824000001</v>
       </c>
       <c r="N57">
-        <v>-210.2136720000001</v>
+        <v>-293.4865824000001</v>
       </c>
       <c r="O57">
-        <v>-73.57478520000002</v>
+        <v>-102.72030384</v>
       </c>
       <c r="P57">
-        <v>-136.6388868</v>
+        <v>-190.76627856</v>
       </c>
       <c r="Q57">
-        <v>-113.0388868</v>
+        <v>-167.1662785600001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1726967916980563</v>
+        <v>0.1776600814471446</v>
       </c>
       <c r="T57">
-        <v>1.846502938244813</v>
+        <v>1.918724851678677</v>
       </c>
       <c r="U57">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1771324676806904</v>
+        <v>0.1481469596711457</v>
       </c>
       <c r="W57">
-        <v>0.1652318004897174</v>
+        <v>0.2008669469095438</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.5060927648019727</v>
+        <v>0.4232770276318449</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1906559261060882</v>
+        <v>0.1925559261060882</v>
       </c>
       <c r="C58">
-        <v>-422.8124373621411</v>
+        <v>-482.2362008903285</v>
       </c>
       <c r="D58">
-        <v>1613.215562637859</v>
+        <v>1592.329799109672</v>
       </c>
       <c r="E58">
-        <v>2032.028</v>
+        <v>2070.566</v>
       </c>
       <c r="F58">
-        <v>2158.128</v>
+        <v>2196.666</v>
       </c>
       <c r="G58">
         <v>122.1</v>
@@ -6049,37 +6049,37 @@
         <v>215.4</v>
       </c>
       <c r="M58">
-        <v>508.8865824000001</v>
+        <v>517.9738428000001</v>
       </c>
       <c r="N58">
-        <v>-293.4865824000001</v>
+        <v>-302.5738428000001</v>
       </c>
       <c r="O58">
-        <v>-102.72030384</v>
+        <v>-105.90084498</v>
       </c>
       <c r="P58">
-        <v>-190.76627856</v>
+        <v>-196.6729978200001</v>
       </c>
       <c r="Q58">
-        <v>-167.1662785600001</v>
+        <v>-173.0729978200001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1776600814471446</v>
+        <v>0.1807265949691712</v>
       </c>
       <c r="T58">
-        <v>1.918724851678677</v>
+        <v>1.96334635985725</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1481469596711457</v>
+        <v>0.1455478902032309</v>
       </c>
       <c r="W58">
-        <v>0.2008669469095438</v>
+        <v>0.2014798074900782</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4232770276318449</v>
+        <v>0.415851114866374</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1925559261060882</v>
+        <v>0.1944559261060882</v>
       </c>
       <c r="C59">
-        <v>-482.2362008903285</v>
+        <v>-541.1260744923895</v>
       </c>
       <c r="D59">
-        <v>1592.329799109672</v>
+        <v>1571.977925507611</v>
       </c>
       <c r="E59">
-        <v>2070.566</v>
+        <v>2109.104</v>
       </c>
       <c r="F59">
-        <v>2196.666</v>
+        <v>2235.204</v>
       </c>
       <c r="G59">
         <v>122.1</v>
@@ -6131,37 +6131,37 @@
         <v>215.4</v>
       </c>
       <c r="M59">
-        <v>517.9738428000001</v>
+        <v>527.0611032</v>
       </c>
       <c r="N59">
-        <v>-302.5738428000001</v>
+        <v>-311.6611032000001</v>
       </c>
       <c r="O59">
-        <v>-105.90084498</v>
+        <v>-109.08138612</v>
       </c>
       <c r="P59">
-        <v>-196.6729978200001</v>
+        <v>-202.5797170800001</v>
       </c>
       <c r="Q59">
-        <v>-173.0729978200001</v>
+        <v>-178.9797170800001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1807265949691712</v>
+        <v>0.1839391329446277</v>
       </c>
       <c r="T59">
-        <v>1.96334635985725</v>
+        <v>2.010092701758614</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.1455478902032309</v>
+        <v>0.1430384438204166</v>
       </c>
       <c r="W59">
-        <v>0.2014798074900782</v>
+        <v>0.2020715349471458</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.415851114866374</v>
+        <v>0.408681268058333</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1944559261060882</v>
+        <v>0.1963559261060882</v>
       </c>
       <c r="C60">
-        <v>-541.1260744923886</v>
+        <v>-599.5022710729727</v>
       </c>
       <c r="D60">
-        <v>1571.977925507611</v>
+        <v>1552.139728927027</v>
       </c>
       <c r="E60">
-        <v>2109.104</v>
+        <v>2147.642</v>
       </c>
       <c r="F60">
-        <v>2235.204</v>
+        <v>2273.742</v>
       </c>
       <c r="G60">
         <v>122.1</v>
@@ -6213,37 +6213,37 @@
         <v>215.4</v>
       </c>
       <c r="M60">
-        <v>527.0611031999999</v>
+        <v>536.1483635999999</v>
       </c>
       <c r="N60">
-        <v>-311.6611032</v>
+        <v>-320.7483635999999</v>
       </c>
       <c r="O60">
-        <v>-109.08138612</v>
+        <v>-112.26192726</v>
       </c>
       <c r="P60">
-        <v>-202.57971708</v>
+        <v>-208.48643634</v>
       </c>
       <c r="Q60">
-        <v>-178.97971708</v>
+        <v>-184.88643634</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1839391329446277</v>
+        <v>0.1873083800896186</v>
       </c>
       <c r="T60">
-        <v>2.010092701758613</v>
+        <v>2.059119353021018</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1430384438204166</v>
+        <v>0.1406140634166808</v>
       </c>
       <c r="W60">
-        <v>0.2020715349471458</v>
+        <v>0.2026432038463467</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4086812680583332</v>
+        <v>0.4017544669048021</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1963559261060882</v>
+        <v>0.1982559261060882</v>
       </c>
       <c r="C61">
-        <v>-599.5022710729727</v>
+        <v>-657.3839959138768</v>
       </c>
       <c r="D61">
-        <v>1552.139728927027</v>
+        <v>1532.796004086123</v>
       </c>
       <c r="E61">
-        <v>2147.642</v>
+        <v>2186.18</v>
       </c>
       <c r="F61">
-        <v>2273.742</v>
+        <v>2312.28</v>
       </c>
       <c r="G61">
         <v>122.1</v>
@@ -6295,37 +6295,37 @@
         <v>215.4</v>
       </c>
       <c r="M61">
-        <v>536.1483635999999</v>
+        <v>545.2356239999999</v>
       </c>
       <c r="N61">
-        <v>-320.7483635999999</v>
+        <v>-329.8356239999999</v>
       </c>
       <c r="O61">
-        <v>-112.26192726</v>
+        <v>-115.4424684</v>
       </c>
       <c r="P61">
-        <v>-208.48643634</v>
+        <v>-214.3931556</v>
       </c>
       <c r="Q61">
-        <v>-184.88643634</v>
+        <v>-190.7931556</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1873083800896186</v>
+        <v>0.1908460895918591</v>
       </c>
       <c r="T61">
-        <v>2.059119353021018</v>
+        <v>2.110597336846544</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1406140634166808</v>
+        <v>0.1382704956930694</v>
       </c>
       <c r="W61">
-        <v>0.2026432038463467</v>
+        <v>0.2031958171155742</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4017544669048021</v>
+        <v>0.3950585591230554</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1982559261060882</v>
+        <v>0.2001559261060882</v>
       </c>
       <c r="C62">
-        <v>-657.3839959138768</v>
+        <v>-714.7895086892661</v>
       </c>
       <c r="D62">
-        <v>1532.796004086123</v>
+        <v>1513.928491310734</v>
       </c>
       <c r="E62">
-        <v>2186.18</v>
+        <v>2224.718</v>
       </c>
       <c r="F62">
-        <v>2312.28</v>
+        <v>2350.818</v>
       </c>
       <c r="G62">
         <v>122.1</v>
@@ -6377,37 +6377,37 @@
         <v>215.4</v>
       </c>
       <c r="M62">
-        <v>545.2356239999999</v>
+        <v>554.3228844</v>
       </c>
       <c r="N62">
-        <v>-329.8356239999999</v>
+        <v>-338.9228844</v>
       </c>
       <c r="O62">
-        <v>-115.4424684</v>
+        <v>-118.62300954</v>
       </c>
       <c r="P62">
-        <v>-214.3931556</v>
+        <v>-220.29987486</v>
       </c>
       <c r="Q62">
-        <v>-190.7931556</v>
+        <v>-196.6998748600001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1908460895918591</v>
+        <v>0.1945652200942145</v>
       </c>
       <c r="T62">
-        <v>2.110597336846544</v>
+        <v>2.164715217278507</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1382704956930694</v>
+        <v>0.1360037662554781</v>
       </c>
       <c r="W62">
-        <v>0.2031958171155742</v>
+        <v>0.2037303119169583</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3950585591230554</v>
+        <v>0.3885821893013659</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2001559261060882</v>
+        <v>0.2020559261060882</v>
       </c>
       <c r="C63">
-        <v>-714.7895086892661</v>
+        <v>-771.7361809564372</v>
       </c>
       <c r="D63">
-        <v>1513.928491310734</v>
+        <v>1495.519819043563</v>
       </c>
       <c r="E63">
-        <v>2224.718</v>
+        <v>2263.256</v>
       </c>
       <c r="F63">
-        <v>2350.818</v>
+        <v>2389.356</v>
       </c>
       <c r="G63">
         <v>122.1</v>
@@ -6459,37 +6459,37 @@
         <v>215.4</v>
       </c>
       <c r="M63">
-        <v>554.3228844</v>
+        <v>563.4101448</v>
       </c>
       <c r="N63">
-        <v>-338.9228844</v>
+        <v>-348.0101448</v>
       </c>
       <c r="O63">
-        <v>-118.62300954</v>
+        <v>-121.80355068</v>
       </c>
       <c r="P63">
-        <v>-220.29987486</v>
+        <v>-226.20659412</v>
       </c>
       <c r="Q63">
-        <v>-196.6998748600001</v>
+        <v>-202.60659412</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1945652200942145</v>
+        <v>0.1984800943072201</v>
       </c>
       <c r="T63">
-        <v>2.164715217278507</v>
+        <v>2.221681407206888</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1360037662554781</v>
+        <v>0.1338101571223252</v>
       </c>
       <c r="W63">
-        <v>0.2037303119169583</v>
+        <v>0.2042475649505557</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3885821893013659</v>
+        <v>0.3823147346352148</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2020559261060882</v>
+        <v>0.2039559261060881</v>
       </c>
       <c r="C64">
-        <v>-771.7361809564372</v>
+        <v>-828.2405495026071</v>
       </c>
       <c r="D64">
-        <v>1495.519819043563</v>
+        <v>1477.553450497393</v>
       </c>
       <c r="E64">
-        <v>2263.256</v>
+        <v>2301.794</v>
       </c>
       <c r="F64">
-        <v>2389.356</v>
+        <v>2427.894</v>
       </c>
       <c r="G64">
         <v>122.1</v>
@@ -6541,37 +6541,37 @@
         <v>215.4</v>
       </c>
       <c r="M64">
-        <v>563.4101448</v>
+        <v>572.4974052</v>
       </c>
       <c r="N64">
-        <v>-348.0101448</v>
+        <v>-357.0974052</v>
       </c>
       <c r="O64">
-        <v>-121.80355068</v>
+        <v>-124.98409182</v>
       </c>
       <c r="P64">
-        <v>-226.20659412</v>
+        <v>-232.11331338</v>
       </c>
       <c r="Q64">
-        <v>-202.60659412</v>
+        <v>-208.51331338</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1984800943072201</v>
+        <v>0.2026065833425503</v>
       </c>
       <c r="T64">
-        <v>2.221681407206888</v>
+        <v>2.281726850644912</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1338101571223252</v>
+        <v>0.1316861863743518</v>
       </c>
       <c r="W64">
-        <v>0.2042475649505557</v>
+        <v>0.2047483972529278</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3823147346352148</v>
+        <v>0.3762462467838622</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2039559261060881</v>
+        <v>0.2058559261060882</v>
       </c>
       <c r="C65">
-        <v>-828.2405495026071</v>
+        <v>-884.318365892063</v>
       </c>
       <c r="D65">
-        <v>1477.553450497393</v>
+        <v>1460.013634107937</v>
       </c>
       <c r="E65">
-        <v>2301.794</v>
+        <v>2340.332</v>
       </c>
       <c r="F65">
-        <v>2427.894</v>
+        <v>2466.432</v>
       </c>
       <c r="G65">
         <v>122.1</v>
@@ -6623,37 +6623,37 @@
         <v>215.4</v>
       </c>
       <c r="M65">
-        <v>572.4974052</v>
+        <v>581.5846656</v>
       </c>
       <c r="N65">
-        <v>-357.0974052</v>
+        <v>-366.1846656</v>
       </c>
       <c r="O65">
-        <v>-124.98409182</v>
+        <v>-128.16463296</v>
       </c>
       <c r="P65">
-        <v>-232.11331338</v>
+        <v>-238.02003264</v>
       </c>
       <c r="Q65">
-        <v>-208.51331338</v>
+        <v>-214.42003264</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2026065833425503</v>
+        <v>0.2069623217687323</v>
       </c>
       <c r="T65">
-        <v>2.281726850644912</v>
+        <v>2.345108152051716</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1316861863743518</v>
+        <v>0.1296285897122526</v>
       </c>
       <c r="W65">
-        <v>0.2047483972529278</v>
+        <v>0.2052335785458509</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3762462467838622</v>
+        <v>0.3703673991778644</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2058559261060882</v>
+        <v>0.2077559261060882</v>
       </c>
       <c r="C66">
-        <v>-884.318365892063</v>
+        <v>-939.9846425257192</v>
       </c>
       <c r="D66">
-        <v>1460.013634107937</v>
+        <v>1442.885357474281</v>
       </c>
       <c r="E66">
-        <v>2340.332</v>
+        <v>2378.87</v>
       </c>
       <c r="F66">
-        <v>2466.432</v>
+        <v>2504.97</v>
       </c>
       <c r="G66">
         <v>122.1</v>
@@ -6705,37 +6705,37 @@
         <v>215.4</v>
       </c>
       <c r="M66">
-        <v>581.5846656</v>
+        <v>590.671926</v>
       </c>
       <c r="N66">
-        <v>-366.1846656</v>
+        <v>-375.271926</v>
       </c>
       <c r="O66">
-        <v>-128.16463296</v>
+        <v>-131.3451741</v>
       </c>
       <c r="P66">
-        <v>-238.02003264</v>
+        <v>-243.9267519</v>
       </c>
       <c r="Q66">
-        <v>-214.42003264</v>
+        <v>-220.3267519</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2069623217687323</v>
+        <v>0.2115669595335532</v>
       </c>
       <c r="T66">
-        <v>2.345108152051716</v>
+        <v>2.412111242110336</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.1296285897122526</v>
+        <v>0.1276343037166794</v>
       </c>
       <c r="W66">
-        <v>0.2052335785458509</v>
+        <v>0.205703831183607</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3703673991778644</v>
+        <v>0.3646694391905126</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2077559261060882</v>
+        <v>0.2096559261060882</v>
       </c>
       <c r="C67">
-        <v>-939.9846425257192</v>
+        <v>-995.2536954961574</v>
       </c>
       <c r="D67">
-        <v>1442.885357474281</v>
+        <v>1426.154304503842</v>
       </c>
       <c r="E67">
-        <v>2378.87</v>
+        <v>2417.408</v>
       </c>
       <c r="F67">
-        <v>2504.97</v>
+        <v>2543.508</v>
       </c>
       <c r="G67">
         <v>122.1</v>
@@ -6787,37 +6787,37 @@
         <v>215.4</v>
       </c>
       <c r="M67">
-        <v>590.671926</v>
+        <v>599.7591864</v>
       </c>
       <c r="N67">
-        <v>-375.271926</v>
+        <v>-384.3591864</v>
       </c>
       <c r="O67">
-        <v>-131.3451741</v>
+        <v>-134.52571524</v>
       </c>
       <c r="P67">
-        <v>-243.9267519</v>
+        <v>-249.83347116</v>
       </c>
       <c r="Q67">
-        <v>-220.3267519</v>
+        <v>-226.23347116</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2115669595335532</v>
+        <v>0.2164424583433636</v>
       </c>
       <c r="T67">
-        <v>2.412111242110336</v>
+        <v>2.483055690407699</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1276343037166794</v>
+        <v>0.1257004506300631</v>
       </c>
       <c r="W67">
-        <v>0.205703831183607</v>
+        <v>0.2061598337414311</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3646694391905126</v>
+        <v>0.359144144657323</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2096559261060882</v>
+        <v>0.2115559261060882</v>
       </c>
       <c r="C68">
-        <v>-995.2536954961574</v>
+        <v>-1050.139184495272</v>
       </c>
       <c r="D68">
-        <v>1426.154304503842</v>
+        <v>1409.806815504728</v>
       </c>
       <c r="E68">
-        <v>2417.408</v>
+        <v>2455.946</v>
       </c>
       <c r="F68">
-        <v>2543.508</v>
+        <v>2582.046</v>
       </c>
       <c r="G68">
         <v>122.1</v>
@@ -6869,37 +6869,37 @@
         <v>215.4</v>
       </c>
       <c r="M68">
-        <v>599.7591864</v>
+        <v>608.8464468</v>
       </c>
       <c r="N68">
-        <v>-384.3591864</v>
+        <v>-393.4464468</v>
       </c>
       <c r="O68">
-        <v>-134.52571524</v>
+        <v>-137.70625638</v>
       </c>
       <c r="P68">
-        <v>-249.83347116</v>
+        <v>-255.74019042</v>
       </c>
       <c r="Q68">
-        <v>-226.23347116</v>
+        <v>-232.14019042</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2164424583433636</v>
+        <v>0.2216134419295262</v>
       </c>
       <c r="T68">
-        <v>2.483055690407699</v>
+        <v>2.558299802238236</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1257004506300631</v>
+        <v>0.1238243245012562</v>
       </c>
       <c r="W68">
-        <v>0.2061598337414311</v>
+        <v>0.2066022242826038</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.359144144657323</v>
+        <v>0.3537837842893033</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2115559261060882</v>
+        <v>0.2134559261060882</v>
       </c>
       <c r="C69">
-        <v>-1050.139184495272</v>
+        <v>-1104.654150008343</v>
       </c>
       <c r="D69">
-        <v>1409.806815504728</v>
+        <v>1393.829849991657</v>
       </c>
       <c r="E69">
-        <v>2455.946</v>
+        <v>2494.484</v>
       </c>
       <c r="F69">
-        <v>2582.046</v>
+        <v>2620.584</v>
       </c>
       <c r="G69">
         <v>122.1</v>
@@ -6951,37 +6951,37 @@
         <v>215.4</v>
       </c>
       <c r="M69">
-        <v>608.8464468</v>
+        <v>617.9337072</v>
       </c>
       <c r="N69">
-        <v>-393.4464468</v>
+        <v>-402.5337072</v>
       </c>
       <c r="O69">
-        <v>-137.70625638</v>
+        <v>-140.88679752</v>
       </c>
       <c r="P69">
-        <v>-255.74019042</v>
+        <v>-261.64690968</v>
       </c>
       <c r="Q69">
-        <v>-232.14019042</v>
+        <v>-238.04690968</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2216134419295262</v>
+        <v>0.2271076119898239</v>
       </c>
       <c r="T69">
-        <v>2.558299802238236</v>
+        <v>2.638246671058181</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1238243245012562</v>
+        <v>0.1220033785527083</v>
       </c>
       <c r="W69">
-        <v>0.2066022242826038</v>
+        <v>0.2070316033372714</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3537837842893033</v>
+        <v>0.3485810815791666</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2134559261060882</v>
+        <v>0.2153559261060882</v>
       </c>
       <c r="C70">
-        <v>-1104.654150008343</v>
+        <v>-1158.811048007385</v>
       </c>
       <c r="D70">
-        <v>1393.829849991657</v>
+        <v>1378.210951992615</v>
       </c>
       <c r="E70">
-        <v>2494.484</v>
+        <v>2533.022</v>
       </c>
       <c r="F70">
-        <v>2620.584</v>
+        <v>2659.122</v>
       </c>
       <c r="G70">
         <v>122.1</v>
@@ -7033,37 +7033,37 @@
         <v>215.4</v>
       </c>
       <c r="M70">
-        <v>617.9337072</v>
+        <v>627.0209675999999</v>
       </c>
       <c r="N70">
-        <v>-402.5337072</v>
+        <v>-411.6209676</v>
       </c>
       <c r="O70">
-        <v>-140.88679752</v>
+        <v>-144.06733866</v>
       </c>
       <c r="P70">
-        <v>-261.64690968</v>
+        <v>-267.55362894</v>
       </c>
       <c r="Q70">
-        <v>-238.04690968</v>
+        <v>-243.95362894</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2271076119898239</v>
+        <v>0.2329562446346569</v>
       </c>
       <c r="T70">
-        <v>2.638246671058181</v>
+        <v>2.723351402382638</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1220033785527083</v>
+        <v>0.1202352136461473</v>
       </c>
       <c r="W70">
-        <v>0.2070316033372714</v>
+        <v>0.2074485366222385</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3485810815791666</v>
+        <v>0.3435291818461351</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2153559261060882</v>
+        <v>0.2172559261060882</v>
       </c>
       <c r="C71">
-        <v>-1158.811048007385</v>
+        <v>-1212.621782337756</v>
       </c>
       <c r="D71">
-        <v>1378.210951992615</v>
+        <v>1362.938217662244</v>
       </c>
       <c r="E71">
-        <v>2533.022</v>
+        <v>2571.56</v>
       </c>
       <c r="F71">
-        <v>2659.122</v>
+        <v>2697.66</v>
       </c>
       <c r="G71">
         <v>122.1</v>
@@ -7115,37 +7115,37 @@
         <v>215.4</v>
       </c>
       <c r="M71">
-        <v>627.0209675999999</v>
+        <v>636.1082279999999</v>
       </c>
       <c r="N71">
-        <v>-411.6209676</v>
+        <v>-420.708228</v>
       </c>
       <c r="O71">
-        <v>-144.06733866</v>
+        <v>-147.2478798</v>
       </c>
       <c r="P71">
-        <v>-267.55362894</v>
+        <v>-273.4603482</v>
       </c>
       <c r="Q71">
-        <v>-243.95362894</v>
+        <v>-249.8603482</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2329562446346569</v>
+        <v>0.2391947861224788</v>
       </c>
       <c r="T71">
-        <v>2.723351402382638</v>
+        <v>2.814129782462059</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1202352136461473</v>
+        <v>0.1185175677369166</v>
       </c>
       <c r="W71">
-        <v>0.2074485366222385</v>
+        <v>0.2078535575276351</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3435291818461351</v>
+        <v>0.3386216221054761</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2172559261060882</v>
+        <v>0.2191559261060882</v>
       </c>
       <c r="C72">
-        <v>-1212.621782337756</v>
+        <v>-1266.097734975001</v>
       </c>
       <c r="D72">
-        <v>1362.938217662244</v>
+        <v>1348.000265025</v>
       </c>
       <c r="E72">
-        <v>2571.56</v>
+        <v>2610.098</v>
       </c>
       <c r="F72">
-        <v>2697.66</v>
+        <v>2736.198</v>
       </c>
       <c r="G72">
         <v>122.1</v>
@@ -7197,37 +7197,37 @@
         <v>215.4</v>
       </c>
       <c r="M72">
-        <v>636.1082279999999</v>
+        <v>645.1954884000002</v>
       </c>
       <c r="N72">
-        <v>-420.708228</v>
+        <v>-429.7954884000002</v>
       </c>
       <c r="O72">
-        <v>-147.2478798</v>
+        <v>-150.4284209400001</v>
       </c>
       <c r="P72">
-        <v>-273.4603482</v>
+        <v>-279.3670674600002</v>
       </c>
       <c r="Q72">
-        <v>-249.8603482</v>
+        <v>-255.7670674600002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2391947861224788</v>
+        <v>0.2458635718508402</v>
       </c>
       <c r="T72">
-        <v>2.814129782462059</v>
+        <v>2.911168740477993</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1185175677369166</v>
+        <v>0.1168483062194952</v>
       </c>
       <c r="W72">
-        <v>0.2078535575276351</v>
+        <v>0.208247169393443</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3386216221054761</v>
+        <v>0.3338523034842721</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2191559261060882</v>
+        <v>0.2210559261060882</v>
       </c>
       <c r="C73">
-        <v>-1266.097734975</v>
+        <v>-1319.249794313553</v>
       </c>
       <c r="D73">
-        <v>1348.000265025</v>
+        <v>1333.386205686447</v>
       </c>
       <c r="E73">
-        <v>2610.098</v>
+        <v>2648.636</v>
       </c>
       <c r="F73">
-        <v>2736.198</v>
+        <v>2774.736</v>
       </c>
       <c r="G73">
         <v>122.1</v>
@@ -7279,37 +7279,37 @@
         <v>215.4</v>
       </c>
       <c r="M73">
-        <v>645.1954884</v>
+        <v>654.2827488</v>
       </c>
       <c r="N73">
-        <v>-429.7954884000001</v>
+        <v>-438.8827488000001</v>
       </c>
       <c r="O73">
-        <v>-150.42842094</v>
+        <v>-153.60896208</v>
       </c>
       <c r="P73">
-        <v>-279.36706746</v>
+        <v>-285.2737867200001</v>
       </c>
       <c r="Q73">
-        <v>-255.76706746</v>
+        <v>-261.6737867200001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2458635718508401</v>
+        <v>0.2530086994169415</v>
       </c>
       <c r="T73">
-        <v>2.911168740477991</v>
+        <v>3.01513905263792</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1168483062194952</v>
+        <v>0.1152254130775578</v>
       </c>
       <c r="W73">
-        <v>0.208247169393443</v>
+        <v>0.2086298475963119</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3338523034842721</v>
+        <v>0.3292154659358795</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2210559261060882</v>
+        <v>0.2229559261060882</v>
       </c>
       <c r="C74">
-        <v>-1319.249794313553</v>
+        <v>-1372.08838163507</v>
       </c>
       <c r="D74">
-        <v>1333.386205686447</v>
+        <v>1319.08561836493</v>
       </c>
       <c r="E74">
-        <v>2648.636</v>
+        <v>2687.174</v>
       </c>
       <c r="F74">
-        <v>2774.736</v>
+        <v>2813.274</v>
       </c>
       <c r="G74">
         <v>122.1</v>
@@ -7361,37 +7361,37 @@
         <v>215.4</v>
       </c>
       <c r="M74">
-        <v>654.2827488</v>
+        <v>663.3700092</v>
       </c>
       <c r="N74">
-        <v>-438.8827488000001</v>
+        <v>-447.9700092</v>
       </c>
       <c r="O74">
-        <v>-153.60896208</v>
+        <v>-156.78950322</v>
       </c>
       <c r="P74">
-        <v>-285.2737867200001</v>
+        <v>-291.18050598</v>
       </c>
       <c r="Q74">
-        <v>-261.6737867200001</v>
+        <v>-267.58050598</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2530086994169415</v>
+        <v>0.2606830956916431</v>
       </c>
       <c r="T74">
-        <v>3.01513905263792</v>
+        <v>3.126810869402287</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1152254130775578</v>
+        <v>0.1136469827614269</v>
       </c>
       <c r="W74">
-        <v>0.2086298475963119</v>
+        <v>0.2090020414648556</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3292154659358795</v>
+        <v>0.3247056650326482</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2229559261060882</v>
+        <v>0.2248559261060882</v>
       </c>
       <c r="C75">
-        <v>-1372.08838163507</v>
+        <v>-1424.623475891578</v>
       </c>
       <c r="D75">
-        <v>1319.08561836493</v>
+        <v>1305.088524108422</v>
       </c>
       <c r="E75">
-        <v>2687.174</v>
+        <v>2725.712</v>
       </c>
       <c r="F75">
-        <v>2813.274</v>
+        <v>2851.812</v>
       </c>
       <c r="G75">
         <v>122.1</v>
@@ -7443,37 +7443,37 @@
         <v>215.4</v>
       </c>
       <c r="M75">
-        <v>663.3700092</v>
+        <v>672.4572696</v>
       </c>
       <c r="N75">
-        <v>-447.9700092</v>
+        <v>-457.0572696</v>
       </c>
       <c r="O75">
-        <v>-156.78950322</v>
+        <v>-159.97004436</v>
       </c>
       <c r="P75">
-        <v>-291.18050598</v>
+        <v>-297.0872252400001</v>
       </c>
       <c r="Q75">
-        <v>-267.58050598</v>
+        <v>-273.48722524</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2606830956916431</v>
+        <v>0.2689478301413216</v>
       </c>
       <c r="T75">
-        <v>3.126810869402287</v>
+        <v>3.24707282591776</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1136469827614269</v>
+        <v>0.1121112127241103</v>
       </c>
       <c r="W75">
-        <v>0.2090020414648556</v>
+        <v>0.2093641760396548</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3247056650326482</v>
+        <v>0.3203177506403151</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2248559261060882</v>
+        <v>0.2267559261060882</v>
       </c>
       <c r="C76">
-        <v>-1424.623475891578</v>
+        <v>-1476.864636927334</v>
       </c>
       <c r="D76">
-        <v>1305.088524108422</v>
+        <v>1291.385363072666</v>
       </c>
       <c r="E76">
-        <v>2725.712</v>
+        <v>2764.25</v>
       </c>
       <c r="F76">
-        <v>2851.812</v>
+        <v>2890.35</v>
       </c>
       <c r="G76">
         <v>122.1</v>
@@ -7525,37 +7525,37 @@
         <v>215.4</v>
       </c>
       <c r="M76">
-        <v>672.4572696</v>
+        <v>681.54453</v>
       </c>
       <c r="N76">
-        <v>-457.0572696</v>
+        <v>-466.14453</v>
       </c>
       <c r="O76">
-        <v>-159.97004436</v>
+        <v>-163.1505855</v>
       </c>
       <c r="P76">
-        <v>-297.0872252400001</v>
+        <v>-302.9939445</v>
       </c>
       <c r="Q76">
-        <v>-273.48722524</v>
+        <v>-279.3939445</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2689478301413216</v>
+        <v>0.2778737433469745</v>
       </c>
       <c r="T76">
-        <v>3.24707282591776</v>
+        <v>3.37695573895447</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1121112127241103</v>
+        <v>0.1106163965544555</v>
       </c>
       <c r="W76">
-        <v>0.2093641760396548</v>
+        <v>0.2097166536924594</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3203177506403151</v>
+        <v>0.3160468472984442</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2267559261060882</v>
+        <v>0.2286559261060882</v>
       </c>
       <c r="C77">
-        <v>-1476.864636927334</v>
+        <v>-1528.82102725292</v>
       </c>
       <c r="D77">
-        <v>1291.385363072666</v>
+        <v>1277.96697274708</v>
       </c>
       <c r="E77">
-        <v>2764.25</v>
+        <v>2802.788</v>
       </c>
       <c r="F77">
-        <v>2890.35</v>
+        <v>2928.888</v>
       </c>
       <c r="G77">
         <v>122.1</v>
@@ -7607,37 +7607,37 @@
         <v>215.4</v>
       </c>
       <c r="M77">
-        <v>681.54453</v>
+        <v>690.6317904</v>
       </c>
       <c r="N77">
-        <v>-466.14453</v>
+        <v>-475.2317904</v>
       </c>
       <c r="O77">
-        <v>-163.1505855</v>
+        <v>-166.33112664</v>
       </c>
       <c r="P77">
-        <v>-302.9939445</v>
+        <v>-308.90066376</v>
       </c>
       <c r="Q77">
-        <v>-279.3939445</v>
+        <v>-285.30066376</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2778737433469745</v>
+        <v>0.2875434826530984</v>
       </c>
       <c r="T77">
-        <v>3.37695573895447</v>
+        <v>3.517662228077574</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1106163965544555</v>
+        <v>0.1091609176524232</v>
       </c>
       <c r="W77">
-        <v>0.2097166536924594</v>
+        <v>0.2100598556175586</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3160468472984442</v>
+        <v>0.3118883361497805</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2286559261060882</v>
+        <v>0.2305559261060882</v>
       </c>
       <c r="C78">
-        <v>-1528.82102725292</v>
+        <v>-1580.501432475826</v>
       </c>
       <c r="D78">
-        <v>1277.96697274708</v>
+        <v>1264.824567524174</v>
       </c>
       <c r="E78">
-        <v>2802.788</v>
+        <v>2841.326</v>
       </c>
       <c r="F78">
-        <v>2928.888</v>
+        <v>2967.426</v>
       </c>
       <c r="G78">
         <v>122.1</v>
@@ -7689,37 +7689,37 @@
         <v>215.4</v>
       </c>
       <c r="M78">
-        <v>690.6317904</v>
+        <v>699.7190508</v>
       </c>
       <c r="N78">
-        <v>-475.2317904</v>
+        <v>-484.3190508</v>
       </c>
       <c r="O78">
-        <v>-166.33112664</v>
+        <v>-169.51166778</v>
       </c>
       <c r="P78">
-        <v>-308.90066376</v>
+        <v>-314.80738302</v>
       </c>
       <c r="Q78">
-        <v>-285.30066376</v>
+        <v>-291.2073830200001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2875434826530984</v>
+        <v>0.2980540688554071</v>
       </c>
       <c r="T78">
-        <v>3.517662228077574</v>
+        <v>3.670604064080947</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1091609176524232</v>
+        <v>0.1077432433971969</v>
       </c>
       <c r="W78">
-        <v>0.2100598556175586</v>
+        <v>0.210394143206941</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3118883361497805</v>
+        <v>0.3078378382777055</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2305559261060882</v>
+        <v>0.2324559261060882</v>
       </c>
       <c r="C79">
-        <v>-1580.501432475826</v>
+        <v>-1631.914280483224</v>
       </c>
       <c r="D79">
-        <v>1264.824567524174</v>
+        <v>1251.949719516776</v>
       </c>
       <c r="E79">
-        <v>2841.326</v>
+        <v>2879.864</v>
       </c>
       <c r="F79">
-        <v>2967.426</v>
+        <v>3005.964</v>
       </c>
       <c r="G79">
         <v>122.1</v>
@@ -7771,37 +7771,37 @@
         <v>215.4</v>
       </c>
       <c r="M79">
-        <v>699.7190508</v>
+        <v>708.8063112</v>
       </c>
       <c r="N79">
-        <v>-484.3190508</v>
+        <v>-493.4063112</v>
       </c>
       <c r="O79">
-        <v>-169.51166778</v>
+        <v>-172.69220892</v>
       </c>
       <c r="P79">
-        <v>-314.80738302</v>
+        <v>-320.71410228</v>
       </c>
       <c r="Q79">
-        <v>-291.2073830200001</v>
+        <v>-297.11410228</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2980540688554071</v>
+        <v>0.3095201628942892</v>
       </c>
       <c r="T79">
-        <v>3.670604064080947</v>
+        <v>3.837449703357354</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1077432433971969</v>
+        <v>0.1063619197638995</v>
       </c>
       <c r="W79">
-        <v>0.210394143206941</v>
+        <v>0.2107198593196725</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3078378382777055</v>
+        <v>0.3038911993254272</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2324559261060882</v>
+        <v>0.2343559261060882</v>
       </c>
       <c r="C80">
-        <v>-1631.914280483224</v>
+        <v>-1683.067659464967</v>
       </c>
       <c r="D80">
-        <v>1251.949719516776</v>
+        <v>1239.334340535033</v>
       </c>
       <c r="E80">
-        <v>2879.864</v>
+        <v>2918.402</v>
       </c>
       <c r="F80">
-        <v>3005.964</v>
+        <v>3044.502</v>
       </c>
       <c r="G80">
         <v>122.1</v>
@@ -7853,37 +7853,37 @@
         <v>215.4</v>
       </c>
       <c r="M80">
-        <v>708.8063112</v>
+        <v>717.8935716</v>
       </c>
       <c r="N80">
-        <v>-493.4063112</v>
+        <v>-502.4935716</v>
       </c>
       <c r="O80">
-        <v>-172.69220892</v>
+        <v>-175.87275006</v>
       </c>
       <c r="P80">
-        <v>-320.71410228</v>
+        <v>-326.62082154</v>
       </c>
       <c r="Q80">
-        <v>-297.11410228</v>
+        <v>-303.02082154</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3095201628942892</v>
+        <v>0.3220782658892554</v>
       </c>
       <c r="T80">
-        <v>3.837449703357354</v>
+        <v>4.020185403517227</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1063619197638995</v>
+        <v>0.1050155663491666</v>
       </c>
       <c r="W80">
-        <v>0.2107198593196725</v>
+        <v>0.2110373294548665</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3038911993254272</v>
+        <v>0.3000444752833332</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2343559261060882</v>
+        <v>0.2362559261060881</v>
       </c>
       <c r="C81">
-        <v>-1683.067659464967</v>
+        <v>-1733.969334857797</v>
       </c>
       <c r="D81">
-        <v>1239.334340535033</v>
+        <v>1226.970665142203</v>
       </c>
       <c r="E81">
-        <v>2918.402</v>
+        <v>2956.94</v>
       </c>
       <c r="F81">
-        <v>3044.502</v>
+        <v>3083.04</v>
       </c>
       <c r="G81">
         <v>122.1</v>
@@ -7935,37 +7935,37 @@
         <v>215.4</v>
       </c>
       <c r="M81">
-        <v>717.8935716</v>
+        <v>726.9808320000001</v>
       </c>
       <c r="N81">
-        <v>-502.4935716</v>
+        <v>-511.5808320000001</v>
       </c>
       <c r="O81">
-        <v>-175.87275006</v>
+        <v>-179.0532912</v>
       </c>
       <c r="P81">
-        <v>-326.62082154</v>
+        <v>-332.5275408000001</v>
       </c>
       <c r="Q81">
-        <v>-303.02082154</v>
+        <v>-308.9275408000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3220782658892554</v>
+        <v>0.3358921791837182</v>
       </c>
       <c r="T81">
-        <v>4.020185403517227</v>
+        <v>4.221194673693089</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1050155663491666</v>
+        <v>0.103702871769802</v>
       </c>
       <c r="W81">
-        <v>0.2110373294548665</v>
+        <v>0.2113468628366807</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3000444752833332</v>
+        <v>0.2962939193422914</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2362559261060881</v>
+        <v>0.2381559261060882</v>
       </c>
       <c r="C82">
-        <v>-1733.969334857797</v>
+        <v>-1784.62676528535</v>
       </c>
       <c r="D82">
-        <v>1226.970665142203</v>
+        <v>1214.85123471465</v>
       </c>
       <c r="E82">
-        <v>2956.94</v>
+        <v>2995.478</v>
       </c>
       <c r="F82">
-        <v>3083.04</v>
+        <v>3121.578</v>
       </c>
       <c r="G82">
         <v>122.1</v>
@@ -8017,37 +8017,37 @@
         <v>215.4</v>
       </c>
       <c r="M82">
-        <v>726.9808320000001</v>
+        <v>736.0680924000001</v>
       </c>
       <c r="N82">
-        <v>-511.5808320000001</v>
+        <v>-520.6680924000001</v>
       </c>
       <c r="O82">
-        <v>-179.0532912</v>
+        <v>-182.23383234</v>
       </c>
       <c r="P82">
-        <v>-332.5275408000001</v>
+        <v>-338.43426006</v>
       </c>
       <c r="Q82">
-        <v>-308.9275408000001</v>
+        <v>-314.83426006</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3358921791837182</v>
+        <v>0.3511601886144402</v>
       </c>
       <c r="T82">
-        <v>4.221194673693089</v>
+        <v>4.443362814413778</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.103702871769802</v>
+        <v>0.1024225894022736</v>
       </c>
       <c r="W82">
-        <v>0.2113468628366807</v>
+        <v>0.2116487534189439</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2962939193422914</v>
+        <v>0.2926359697207818</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2381559261060882</v>
+        <v>0.2400559261060882</v>
       </c>
       <c r="C83">
-        <v>-1784.62676528535</v>
+        <v>-1835.047117562712</v>
       </c>
       <c r="D83">
-        <v>1214.85123471465</v>
+        <v>1202.968882437288</v>
       </c>
       <c r="E83">
-        <v>2995.478</v>
+        <v>3034.016</v>
       </c>
       <c r="F83">
-        <v>3121.578</v>
+        <v>3160.116</v>
       </c>
       <c r="G83">
         <v>122.1</v>
@@ -8099,37 +8099,37 @@
         <v>215.4</v>
       </c>
       <c r="M83">
-        <v>736.0680924000001</v>
+        <v>745.1553528000001</v>
       </c>
       <c r="N83">
-        <v>-520.6680924000001</v>
+        <v>-529.7553528000001</v>
       </c>
       <c r="O83">
-        <v>-182.23383234</v>
+        <v>-185.41437348</v>
       </c>
       <c r="P83">
-        <v>-338.43426006</v>
+        <v>-344.3409793200001</v>
       </c>
       <c r="Q83">
-        <v>-314.83426006</v>
+        <v>-320.7409793200001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3511601886144402</v>
+        <v>0.3681246435374647</v>
       </c>
       <c r="T83">
-        <v>4.443362814413778</v>
+        <v>4.690216304103433</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1024225894022736</v>
+        <v>0.1011735334339532</v>
       </c>
       <c r="W83">
-        <v>0.2116487534189439</v>
+        <v>0.2119432808162738</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2926359697207818</v>
+        <v>0.2890672383827234</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2400559261060882</v>
+        <v>0.2419559261060882</v>
       </c>
       <c r="C84">
-        <v>-1835.047117562712</v>
+        <v>-1885.237280828964</v>
       </c>
       <c r="D84">
-        <v>1202.968882437288</v>
+        <v>1191.316719171037</v>
       </c>
       <c r="E84">
-        <v>3034.016</v>
+        <v>3072.554</v>
       </c>
       <c r="F84">
-        <v>3160.116</v>
+        <v>3198.654</v>
       </c>
       <c r="G84">
         <v>122.1</v>
@@ -8181,37 +8181,37 @@
         <v>215.4</v>
       </c>
       <c r="M84">
-        <v>745.1553528000001</v>
+        <v>754.2426132000001</v>
       </c>
       <c r="N84">
-        <v>-529.7553528000001</v>
+        <v>-538.8426132000001</v>
       </c>
       <c r="O84">
-        <v>-185.41437348</v>
+        <v>-188.59491462</v>
       </c>
       <c r="P84">
-        <v>-344.3409793200001</v>
+        <v>-350.24769858</v>
       </c>
       <c r="Q84">
-        <v>-320.7409793200001</v>
+        <v>-326.64769858</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3681246435374647</v>
+        <v>0.3870849166867273</v>
       </c>
       <c r="T84">
-        <v>4.690216304103433</v>
+        <v>4.966111380815399</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1011735334339532</v>
+        <v>0.09995457519980919</v>
       </c>
       <c r="W84">
-        <v>0.2119432808162738</v>
+        <v>0.212230711167885</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2890672383827234</v>
+        <v>0.2855845005708834</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2419559261060882</v>
+        <v>0.2438559261060882</v>
       </c>
       <c r="C85">
-        <v>-1885.237280828964</v>
+        <v>-1935.203879866251</v>
       </c>
       <c r="D85">
-        <v>1191.316719171037</v>
+        <v>1179.888120133749</v>
       </c>
       <c r="E85">
-        <v>3072.554</v>
+        <v>3111.092</v>
       </c>
       <c r="F85">
-        <v>3198.654</v>
+        <v>3237.192</v>
       </c>
       <c r="G85">
         <v>122.1</v>
@@ -8263,37 +8263,37 @@
         <v>215.4</v>
       </c>
       <c r="M85">
-        <v>754.2426132000001</v>
+        <v>763.3298736</v>
       </c>
       <c r="N85">
-        <v>-538.8426132000001</v>
+        <v>-547.9298736000001</v>
       </c>
       <c r="O85">
-        <v>-188.59491462</v>
+        <v>-191.77545576</v>
       </c>
       <c r="P85">
-        <v>-350.24769858</v>
+        <v>-356.1544178400001</v>
       </c>
       <c r="Q85">
-        <v>-326.64769858</v>
+        <v>-332.55441784</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3870849166867273</v>
+        <v>0.4084152239796479</v>
       </c>
       <c r="T85">
-        <v>4.966111380815399</v>
+        <v>5.276493342116364</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.09995457519980919</v>
+        <v>0.09876463978076383</v>
       </c>
       <c r="W85">
-        <v>0.212230711167885</v>
+        <v>0.2125112979396959</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2855845005708834</v>
+        <v>0.2821846850878966</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2438559261060882</v>
+        <v>0.2457559261060882</v>
       </c>
       <c r="C86">
-        <v>-1935.20387986625</v>
+        <v>-1984.953287659509</v>
       </c>
       <c r="D86">
-        <v>1179.88812013375</v>
+        <v>1168.676712340491</v>
       </c>
       <c r="E86">
-        <v>3111.092</v>
+        <v>3149.63</v>
       </c>
       <c r="F86">
-        <v>3237.192</v>
+        <v>3275.73</v>
       </c>
       <c r="G86">
         <v>122.1</v>
@@ -8345,37 +8345,37 @@
         <v>215.4</v>
       </c>
       <c r="M86">
-        <v>763.3298735999999</v>
+        <v>772.4171339999999</v>
       </c>
       <c r="N86">
-        <v>-547.9298736</v>
+        <v>-557.0171339999999</v>
       </c>
       <c r="O86">
-        <v>-191.77545576</v>
+        <v>-194.9559969</v>
       </c>
       <c r="P86">
-        <v>-356.15441784</v>
+        <v>-362.0611371</v>
       </c>
       <c r="Q86">
-        <v>-332.5544178399999</v>
+        <v>-338.4611371</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4084152239796476</v>
+        <v>0.4325895722449575</v>
       </c>
       <c r="T86">
-        <v>5.276493342116359</v>
+        <v>5.628259564924117</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.09876463978076386</v>
+        <v>0.09760270284216664</v>
       </c>
       <c r="W86">
-        <v>0.2125112979396959</v>
+        <v>0.2127852826698171</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2821846850878967</v>
+        <v>0.2788648652633332</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2457559261060882</v>
+        <v>0.2476559261060882</v>
       </c>
       <c r="C87">
-        <v>-1984.953287659509</v>
+        <v>-2034.491637246867</v>
       </c>
       <c r="D87">
-        <v>1168.676712340491</v>
+        <v>1157.676362753132</v>
       </c>
       <c r="E87">
-        <v>3149.63</v>
+        <v>3188.168</v>
       </c>
       <c r="F87">
-        <v>3275.73</v>
+        <v>3314.268</v>
       </c>
       <c r="G87">
         <v>122.1</v>
@@ -8427,37 +8427,37 @@
         <v>215.4</v>
       </c>
       <c r="M87">
-        <v>772.4171339999999</v>
+        <v>781.5043943999999</v>
       </c>
       <c r="N87">
-        <v>-557.0171339999999</v>
+        <v>-566.1043943999999</v>
       </c>
       <c r="O87">
-        <v>-194.9559969</v>
+        <v>-198.13653804</v>
       </c>
       <c r="P87">
-        <v>-362.0611371</v>
+        <v>-367.9678563599999</v>
       </c>
       <c r="Q87">
-        <v>-338.4611371</v>
+        <v>-344.3678563599999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4325895722449575</v>
+        <v>0.460217398833883</v>
       </c>
       <c r="T87">
-        <v>5.628259564924117</v>
+        <v>6.03027810527584</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.09760270284216664</v>
+        <v>0.0964677876928391</v>
       </c>
       <c r="W87">
-        <v>0.2127852826698171</v>
+        <v>0.2130528956620285</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2788648652633332</v>
+        <v>0.2756222505509689</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2476559261060882</v>
+        <v>0.2495559261060882</v>
       </c>
       <c r="C88">
-        <v>-2034.491637246867</v>
+        <v>-2083.82483290702</v>
       </c>
       <c r="D88">
-        <v>1157.676362753132</v>
+        <v>1146.881167092979</v>
       </c>
       <c r="E88">
-        <v>3188.168</v>
+        <v>3226.706</v>
       </c>
       <c r="F88">
-        <v>3314.268</v>
+        <v>3352.806</v>
       </c>
       <c r="G88">
         <v>122.1</v>
@@ -8509,37 +8509,37 @@
         <v>215.4</v>
       </c>
       <c r="M88">
-        <v>781.5043943999999</v>
+        <v>790.5916547999999</v>
       </c>
       <c r="N88">
-        <v>-566.1043943999999</v>
+        <v>-575.1916547999999</v>
       </c>
       <c r="O88">
-        <v>-198.13653804</v>
+        <v>-201.31707918</v>
       </c>
       <c r="P88">
-        <v>-367.9678563599999</v>
+        <v>-373.87457562</v>
       </c>
       <c r="Q88">
-        <v>-344.3678563599999</v>
+        <v>-350.27457562</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.460217398833883</v>
+        <v>0.4920956602826432</v>
       </c>
       <c r="T88">
-        <v>6.03027810527584</v>
+        <v>6.494145651835519</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0964677876928391</v>
+        <v>0.09535896254694441</v>
       </c>
       <c r="W88">
-        <v>0.2130528956620285</v>
+        <v>0.2133143566314305</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2756222505509689</v>
+        <v>0.2724541787055554</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2495559261060882</v>
+        <v>0.2514559261060882</v>
       </c>
       <c r="C89">
-        <v>-2083.82483290702</v>
+        <v>-2132.958560726469</v>
       </c>
       <c r="D89">
-        <v>1146.881167092979</v>
+        <v>1136.285439273531</v>
       </c>
       <c r="E89">
-        <v>3226.706</v>
+        <v>3265.244</v>
       </c>
       <c r="F89">
-        <v>3352.806</v>
+        <v>3391.344</v>
       </c>
       <c r="G89">
         <v>122.1</v>
@@ -8591,37 +8591,37 @@
         <v>215.4</v>
       </c>
       <c r="M89">
-        <v>790.5916547999999</v>
+        <v>799.6789151999999</v>
       </c>
       <c r="N89">
-        <v>-575.1916547999999</v>
+        <v>-584.2789151999999</v>
       </c>
       <c r="O89">
-        <v>-201.31707918</v>
+        <v>-204.49762032</v>
       </c>
       <c r="P89">
-        <v>-373.87457562</v>
+        <v>-379.78129488</v>
       </c>
       <c r="Q89">
-        <v>-350.27457562</v>
+        <v>-356.18129488</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4920956602826432</v>
+        <v>0.5292869653061969</v>
       </c>
       <c r="T89">
-        <v>6.494145651835519</v>
+        <v>7.035324456155148</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.09535896254694441</v>
+        <v>0.09427533797254732</v>
       </c>
       <c r="W89">
-        <v>0.2133143566314305</v>
+        <v>0.2135698753060734</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2724541787055554</v>
+        <v>0.2693581084929924</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2514559261060882</v>
+        <v>0.2533559261060881</v>
       </c>
       <c r="C90">
-        <v>-2132.958560726469</v>
+        <v>-2181.898298586347</v>
       </c>
       <c r="D90">
-        <v>1136.285439273531</v>
+        <v>1125.883701413653</v>
       </c>
       <c r="E90">
-        <v>3265.244</v>
+        <v>3303.782</v>
       </c>
       <c r="F90">
-        <v>3391.344</v>
+        <v>3429.882</v>
       </c>
       <c r="G90">
         <v>122.1</v>
@@ -8673,37 +8673,37 @@
         <v>215.4</v>
       </c>
       <c r="M90">
-        <v>799.6789151999999</v>
+        <v>808.7661756</v>
       </c>
       <c r="N90">
-        <v>-584.2789151999999</v>
+        <v>-593.3661756</v>
       </c>
       <c r="O90">
-        <v>-204.49762032</v>
+        <v>-207.67816146</v>
       </c>
       <c r="P90">
-        <v>-379.78129488</v>
+        <v>-385.6880141400001</v>
       </c>
       <c r="Q90">
-        <v>-356.18129488</v>
+        <v>-362.08801414</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5292869653061969</v>
+        <v>0.5732403257885784</v>
       </c>
       <c r="T90">
-        <v>7.035324456155148</v>
+        <v>7.674899406714707</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.09427533797254732</v>
+        <v>0.0932160645121816</v>
       </c>
       <c r="W90">
-        <v>0.2135698753060734</v>
+        <v>0.2138196519880276</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2693581084929924</v>
+        <v>0.2663316128919474</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2533559261060881</v>
+        <v>0.2552559261060882</v>
       </c>
       <c r="C91">
-        <v>-2181.898298586347</v>
+        <v>-2230.649325605704</v>
       </c>
       <c r="D91">
-        <v>1125.883701413653</v>
+        <v>1115.670674394296</v>
       </c>
       <c r="E91">
-        <v>3303.782</v>
+        <v>3342.32</v>
       </c>
       <c r="F91">
-        <v>3429.882</v>
+        <v>3468.42</v>
       </c>
       <c r="G91">
         <v>122.1</v>
@@ -8755,37 +8755,37 @@
         <v>215.4</v>
       </c>
       <c r="M91">
-        <v>808.7661756</v>
+        <v>817.853436</v>
       </c>
       <c r="N91">
-        <v>-593.3661756</v>
+        <v>-602.453436</v>
       </c>
       <c r="O91">
-        <v>-207.67816146</v>
+        <v>-210.8587026</v>
       </c>
       <c r="P91">
-        <v>-385.6880141400001</v>
+        <v>-391.5947334</v>
       </c>
       <c r="Q91">
-        <v>-362.08801414</v>
+        <v>-367.9947334</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5732403257885784</v>
+        <v>0.6259843583674363</v>
       </c>
       <c r="T91">
-        <v>7.674899406714707</v>
+        <v>8.442389347386177</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0932160645121816</v>
+        <v>0.09218033046204627</v>
       </c>
       <c r="W91">
-        <v>0.2138196519880276</v>
+        <v>0.2140638780770495</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2663316128919474</v>
+        <v>0.2633723727487036</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2552559261060882</v>
+        <v>0.2571559261060882</v>
       </c>
       <c r="C92">
-        <v>-2230.649325605704</v>
+        <v>-2279.216731075438</v>
       </c>
       <c r="D92">
-        <v>1115.670674394296</v>
+        <v>1105.641268924561</v>
       </c>
       <c r="E92">
-        <v>3342.32</v>
+        <v>3380.858</v>
       </c>
       <c r="F92">
-        <v>3468.42</v>
+        <v>3506.958</v>
       </c>
       <c r="G92">
         <v>122.1</v>
@@ -8837,37 +8837,37 @@
         <v>215.4</v>
       </c>
       <c r="M92">
-        <v>817.853436</v>
+        <v>826.9406964000001</v>
       </c>
       <c r="N92">
-        <v>-602.453436</v>
+        <v>-611.5406964000001</v>
       </c>
       <c r="O92">
-        <v>-210.8587026</v>
+        <v>-214.03924374</v>
       </c>
       <c r="P92">
-        <v>-391.5947334</v>
+        <v>-397.5014526600001</v>
       </c>
       <c r="Q92">
-        <v>-367.9947334</v>
+        <v>-373.9014526600001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6259843583674363</v>
+        <v>0.6904492870749293</v>
       </c>
       <c r="T92">
-        <v>8.442389347386177</v>
+        <v>9.380432608206865</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.09218033046204627</v>
+        <v>0.09116735979762816</v>
       </c>
       <c r="W92">
-        <v>0.2140638780770495</v>
+        <v>0.2143027365597193</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2633723727487036</v>
+        <v>0.2604781708503662</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2571559261060882</v>
+        <v>0.2590559261060882</v>
       </c>
       <c r="C93">
-        <v>-2279.216731075438</v>
+        <v>-2327.605422914649</v>
       </c>
       <c r="D93">
-        <v>1105.641268924561</v>
+        <v>1095.790577085351</v>
       </c>
       <c r="E93">
-        <v>3380.858</v>
+        <v>3419.396</v>
       </c>
       <c r="F93">
-        <v>3506.958</v>
+        <v>3545.496</v>
       </c>
       <c r="G93">
         <v>122.1</v>
@@ -8919,37 +8919,37 @@
         <v>215.4</v>
       </c>
       <c r="M93">
-        <v>826.9406964000001</v>
+        <v>836.0279568000001</v>
       </c>
       <c r="N93">
-        <v>-611.5406964000001</v>
+        <v>-620.6279568000001</v>
       </c>
       <c r="O93">
-        <v>-214.03924374</v>
+        <v>-217.21978488</v>
       </c>
       <c r="P93">
-        <v>-397.5014526600001</v>
+        <v>-403.4081719200001</v>
       </c>
       <c r="Q93">
-        <v>-373.9014526600001</v>
+        <v>-379.8081719200001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6904492870749293</v>
+        <v>0.7710304479592957</v>
       </c>
       <c r="T93">
-        <v>9.380432608206865</v>
+        <v>10.55298668423273</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09116735979762816</v>
+        <v>0.09017641023461045</v>
       </c>
       <c r="W93">
-        <v>0.2143027365597193</v>
+        <v>0.2145364024666789</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2604781708503662</v>
+        <v>0.2576468863846013</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2590559261060882</v>
+        <v>0.2609559261060882</v>
       </c>
       <c r="C94">
-        <v>-2327.605422914649</v>
+        <v>-2375.820135678934</v>
       </c>
       <c r="D94">
-        <v>1095.790577085351</v>
+        <v>1086.113864321066</v>
       </c>
       <c r="E94">
-        <v>3419.396</v>
+        <v>3457.934</v>
       </c>
       <c r="F94">
-        <v>3545.496</v>
+        <v>3584.034</v>
       </c>
       <c r="G94">
         <v>122.1</v>
@@ -9001,37 +9001,37 @@
         <v>215.4</v>
       </c>
       <c r="M94">
-        <v>836.0279568000001</v>
+        <v>845.1152172000001</v>
       </c>
       <c r="N94">
-        <v>-620.6279568000001</v>
+        <v>-629.7152172000001</v>
       </c>
       <c r="O94">
-        <v>-217.21978488</v>
+        <v>-220.40032602</v>
       </c>
       <c r="P94">
-        <v>-403.4081719200001</v>
+        <v>-409.3148911800001</v>
       </c>
       <c r="Q94">
-        <v>-379.8081719200001</v>
+        <v>-385.7148911800001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7710304479592957</v>
+        <v>0.8746347976677666</v>
       </c>
       <c r="T94">
-        <v>10.55298668423273</v>
+        <v>12.06055621055169</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09017641023461045</v>
+        <v>0.08920677141488347</v>
       </c>
       <c r="W94">
-        <v>0.2145364024666789</v>
+        <v>0.2147650433003705</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2576468863846013</v>
+        <v>0.2548764897568099</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2609559261060882</v>
+        <v>0.2628559261060882</v>
       </c>
       <c r="C95">
-        <v>-2375.820135678934</v>
+        <v>-2423.865438148075</v>
       </c>
       <c r="D95">
-        <v>1086.113864321066</v>
+        <v>1076.606561851926</v>
       </c>
       <c r="E95">
-        <v>3457.934</v>
+        <v>3496.472</v>
       </c>
       <c r="F95">
-        <v>3584.034</v>
+        <v>3622.572</v>
       </c>
       <c r="G95">
         <v>122.1</v>
@@ -9083,37 +9083,37 @@
         <v>215.4</v>
       </c>
       <c r="M95">
-        <v>845.1152172000001</v>
+        <v>854.2024776000001</v>
       </c>
       <c r="N95">
-        <v>-629.7152172000001</v>
+        <v>-638.8024776000001</v>
       </c>
       <c r="O95">
-        <v>-220.40032602</v>
+        <v>-223.58086716</v>
       </c>
       <c r="P95">
-        <v>-409.3148911800001</v>
+        <v>-415.2216104400001</v>
       </c>
       <c r="Q95">
-        <v>-385.7148911800001</v>
+        <v>-391.62161044</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8746347976677666</v>
+        <v>1.012773930612395</v>
       </c>
       <c r="T95">
-        <v>12.06055621055169</v>
+        <v>14.07064891231031</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08920677141488347</v>
+        <v>0.08825776320834215</v>
       </c>
       <c r="W95">
-        <v>0.2147650433003705</v>
+        <v>0.2149888194354729</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2548764897568099</v>
+        <v>0.2521650377381204</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2628559261060882</v>
+        <v>0.2647559261060882</v>
       </c>
       <c r="C96">
-        <v>-2423.865438148075</v>
+        <v>-2471.745740518679</v>
       </c>
       <c r="D96">
-        <v>1076.606561851926</v>
+        <v>1067.264259481321</v>
       </c>
       <c r="E96">
-        <v>3496.472</v>
+        <v>3535.01</v>
       </c>
       <c r="F96">
-        <v>3622.572</v>
+        <v>3661.11</v>
       </c>
       <c r="G96">
         <v>122.1</v>
@@ -9165,37 +9165,37 @@
         <v>215.4</v>
       </c>
       <c r="M96">
-        <v>854.2024776000001</v>
+        <v>863.2897380000001</v>
       </c>
       <c r="N96">
-        <v>-638.8024776000001</v>
+        <v>-647.8897380000001</v>
       </c>
       <c r="O96">
-        <v>-223.58086716</v>
+        <v>-226.7614083</v>
       </c>
       <c r="P96">
-        <v>-415.2216104400001</v>
+        <v>-421.1283297000001</v>
       </c>
       <c r="Q96">
-        <v>-391.62161044</v>
+        <v>-397.5283297000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.012773930612395</v>
+        <v>1.206168716734874</v>
       </c>
       <c r="T96">
-        <v>14.07064891231031</v>
+        <v>16.88477869477238</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08825776320834215</v>
+        <v>0.08732873412193856</v>
       </c>
       <c r="W96">
-        <v>0.2149888194354729</v>
+        <v>0.2152078844940469</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2521650377381204</v>
+        <v>0.2495106689198244</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2647559261060882</v>
+        <v>0.2666559261060882</v>
       </c>
       <c r="C97">
-        <v>-2471.745740518679</v>
+        <v>-2519.465301225546</v>
       </c>
       <c r="D97">
-        <v>1067.264259481321</v>
+        <v>1058.082698774454</v>
       </c>
       <c r="E97">
-        <v>3535.01</v>
+        <v>3573.548</v>
       </c>
       <c r="F97">
-        <v>3661.11</v>
+        <v>3699.648</v>
       </c>
       <c r="G97">
         <v>122.1</v>
@@ -9247,37 +9247,37 @@
         <v>215.4</v>
       </c>
       <c r="M97">
-        <v>863.2897380000001</v>
+        <v>872.3769984</v>
       </c>
       <c r="N97">
-        <v>-647.8897380000001</v>
+        <v>-656.9769984000001</v>
       </c>
       <c r="O97">
-        <v>-226.7614083</v>
+        <v>-229.94194944</v>
       </c>
       <c r="P97">
-        <v>-421.1283297000001</v>
+        <v>-427.03504896</v>
       </c>
       <c r="Q97">
-        <v>-397.5283297000001</v>
+        <v>-403.43504896</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.206168716734874</v>
+        <v>1.496260895918593</v>
       </c>
       <c r="T97">
-        <v>16.88477869477238</v>
+        <v>21.10597336846548</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08732873412193856</v>
+        <v>0.08641905980816836</v>
       </c>
       <c r="W97">
-        <v>0.2152078844940469</v>
+        <v>0.2154223856972339</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2495106689198244</v>
+        <v>0.2469115994519095</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2666559261060882</v>
+        <v>0.2685559261060882</v>
       </c>
       <c r="C98">
-        <v>-2519.465301225546</v>
+        <v>-2567.028233413945</v>
       </c>
       <c r="D98">
-        <v>1058.082698774454</v>
+        <v>1049.057766586055</v>
       </c>
       <c r="E98">
-        <v>3573.548</v>
+        <v>3612.086</v>
       </c>
       <c r="F98">
-        <v>3699.648</v>
+        <v>3738.186</v>
       </c>
       <c r="G98">
         <v>122.1</v>
@@ -9329,37 +9329,37 @@
         <v>215.4</v>
       </c>
       <c r="M98">
-        <v>872.3769983999999</v>
+        <v>881.4642587999999</v>
       </c>
       <c r="N98">
-        <v>-656.9769984</v>
+        <v>-666.0642587999999</v>
       </c>
       <c r="O98">
-        <v>-229.94194944</v>
+        <v>-233.12249058</v>
       </c>
       <c r="P98">
-        <v>-427.03504896</v>
+        <v>-432.94176822</v>
       </c>
       <c r="Q98">
-        <v>-403.43504896</v>
+        <v>-409.3417682199999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.496260895918589</v>
+        <v>1.979747861224786</v>
       </c>
       <c r="T98">
-        <v>21.10597336846542</v>
+        <v>28.14129782462057</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08641905980816837</v>
+        <v>0.08552814166581613</v>
       </c>
       <c r="W98">
-        <v>0.2154223856972339</v>
+        <v>0.2156324641952006</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2469115994519097</v>
+        <v>0.2443661190451889</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2685559261060882</v>
+        <v>0.2704559261060882</v>
       </c>
       <c r="C99">
-        <v>-2567.028233413945</v>
+        <v>-2614.438511083451</v>
       </c>
       <c r="D99">
-        <v>1049.057766586055</v>
+        <v>1040.185488916548</v>
       </c>
       <c r="E99">
-        <v>3612.086</v>
+        <v>3650.624</v>
       </c>
       <c r="F99">
-        <v>3738.186</v>
+        <v>3776.724</v>
       </c>
       <c r="G99">
         <v>122.1</v>
@@ -9411,37 +9411,37 @@
         <v>215.4</v>
       </c>
       <c r="M99">
-        <v>881.4642587999999</v>
+        <v>890.5515191999999</v>
       </c>
       <c r="N99">
-        <v>-666.0642587999999</v>
+        <v>-675.1515191999999</v>
       </c>
       <c r="O99">
-        <v>-233.12249058</v>
+        <v>-236.30303172</v>
       </c>
       <c r="P99">
-        <v>-432.94176822</v>
+        <v>-438.84848748</v>
       </c>
       <c r="Q99">
-        <v>-409.3417682199999</v>
+        <v>-415.24848748</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.979747861224786</v>
+        <v>2.946721791837179</v>
       </c>
       <c r="T99">
-        <v>28.14129782462057</v>
+        <v>42.21194673693085</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08552814166581613</v>
+        <v>0.08465540552636902</v>
       </c>
       <c r="W99">
-        <v>0.2156324641952006</v>
+        <v>0.2158382553768822</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2443661190451889</v>
+        <v>0.2418725872181972</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2704559261060882</v>
+        <v>0.2723559261060882</v>
       </c>
       <c r="C100">
-        <v>-2614.438511083451</v>
+        <v>-2661.699974922645</v>
       </c>
       <c r="D100">
-        <v>1040.185488916548</v>
+        <v>1031.462025077355</v>
       </c>
       <c r="E100">
-        <v>3650.624</v>
+        <v>3689.162</v>
       </c>
       <c r="F100">
-        <v>3776.724</v>
+        <v>3815.262</v>
       </c>
       <c r="G100">
         <v>122.1</v>
@@ -9493,37 +9493,37 @@
         <v>215.4</v>
       </c>
       <c r="M100">
-        <v>890.5515191999999</v>
+        <v>899.6387796</v>
       </c>
       <c r="N100">
-        <v>-675.1515191999999</v>
+        <v>-684.2387796</v>
       </c>
       <c r="O100">
-        <v>-236.30303172</v>
+        <v>-239.48357286</v>
       </c>
       <c r="P100">
-        <v>-438.84848748</v>
+        <v>-444.7552067400001</v>
       </c>
       <c r="Q100">
-        <v>-415.24848748</v>
+        <v>-421.15520674</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.946721791837179</v>
+        <v>5.847643583674357</v>
       </c>
       <c r="T100">
-        <v>42.21194673693085</v>
+        <v>84.4238934738617</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08465540552636902</v>
+        <v>0.08380030042004205</v>
       </c>
       <c r="W100">
-        <v>0.2158382553768822</v>
+        <v>0.2160398891609541</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2418725872181972</v>
+        <v>0.2394294297715487</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2723559261060882</v>
-      </c>
-      <c r="C101">
-        <v>-2661.699974922645</v>
-      </c>
-      <c r="D101">
-        <v>1031.462025077355</v>
-      </c>
-      <c r="E101">
-        <v>3689.162</v>
-      </c>
-      <c r="F101">
-        <v>3815.262</v>
-      </c>
-      <c r="G101">
-        <v>122.1</v>
-      </c>
-      <c r="H101">
-        <v>3727.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>239</v>
-      </c>
-      <c r="K101">
-        <v>23.59999999999999</v>
-      </c>
-      <c r="L101">
-        <v>215.4</v>
-      </c>
-      <c r="M101">
-        <v>899.6387796</v>
-      </c>
-      <c r="N101">
-        <v>-684.2387796</v>
-      </c>
-      <c r="O101">
-        <v>-239.48357286</v>
-      </c>
-      <c r="P101">
-        <v>-444.7552067400001</v>
-      </c>
-      <c r="Q101">
-        <v>-421.15520674</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.847643583674357</v>
-      </c>
-      <c r="T101">
-        <v>84.4238934738617</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08380030042004205</v>
-      </c>
-      <c r="W101">
-        <v>0.2160398891609541</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2394294297715487</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
